--- a/resources/CHPC_Student_Cluster_Competition_Parts_List_2026.xlsx
+++ b/resources/CHPC_Student_Cluster_Competition_Parts_List_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/ntuli_hpe_com/Documents/Downloads FY2026/CSIR CHPC Student Cluster 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{BCEA55F5-B1CB-463F-AB31-513E363F5A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302BDDD4-C31B-46EC-B390-2FD3058E1859}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{397F30BA-23C6-48E6-A636-D2979914AF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F478679D-D843-4399-992D-797380CB1E2A}"/>
   </bookViews>
@@ -1485,7 +1485,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1682,7 +1682,6 @@
     <xf numFmtId="165" fontId="19" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1747,26 +1746,8 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1780,11 +1761,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1792,13 +1785,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1824,6 +1814,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3730,74 +3729,74 @@
       <c r="I6" s="10"/>
     </row>
     <row r="8" spans="1:9" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="148" t="s">
+      <c r="B8" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="148"/>
-      <c r="D8" s="148"/>
-      <c r="E8" s="148"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
       <c r="F8" s="24"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="146" t="s">
+      <c r="A11" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="147" t="s">
+      <c r="D11" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147" t="s">
+      <c r="E11" s="144"/>
+      <c r="F11" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="146"/>
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="147"/>
+      <c r="A12" s="150"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="149" t="s">
+      <c r="A13" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="149"/>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="154"/>
+      <c r="D13" s="154"/>
     </row>
     <row r="14" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A14" s="124">
-        <v>1</v>
-      </c>
-      <c r="B14" s="124" t="s">
+      <c r="A14" s="123">
+        <v>1</v>
+      </c>
+      <c r="B14" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="124" t="s">
+      <c r="C14" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
+      <c r="D14" s="123"/>
+      <c r="E14" s="123"/>
+      <c r="F14" s="123"/>
       <c r="G14" s="27" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="150" t="s">
+      <c r="A15" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="151"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127">
+      <c r="B15" s="152"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="126">
         <v>85000</v>
       </c>
     </row>
@@ -3808,42 +3807,42 @@
       <c r="D17" s="7"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="146" t="s">
+      <c r="A18" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="146" t="s">
+      <c r="C18" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="147" t="s">
+      <c r="D18" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="147"/>
-      <c r="F18" s="147" t="s">
+      <c r="E18" s="144"/>
+      <c r="F18" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="146"/>
-      <c r="B19" s="146"/>
-      <c r="C19" s="146"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="147"/>
-      <c r="F19" s="147"/>
+      <c r="A19" s="150"/>
+      <c r="B19" s="150"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="144"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="144"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="145" t="s">
+      <c r="A20" s="149" t="s">
         <v>212</v>
       </c>
-      <c r="B20" s="145"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
       <c r="F20" s="37"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="116">
+      <c r="A21" s="115">
         <v>1</v>
       </c>
       <c r="B21" s="44" t="s">
@@ -3853,15 +3852,15 @@
         <v>163</v>
       </c>
       <c r="D21" s="44"/>
-      <c r="E21" s="128">
+      <c r="E21" s="127">
         <v>33269</v>
       </c>
-      <c r="F21" s="117" t="s">
+      <c r="F21" s="116" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="116">
+      <c r="A22" s="115">
         <v>1</v>
       </c>
       <c r="B22" s="44" t="s">
@@ -3871,15 +3870,15 @@
         <v>13</v>
       </c>
       <c r="D22" s="44"/>
-      <c r="E22" s="128">
+      <c r="E22" s="127">
         <v>46560</v>
       </c>
-      <c r="F22" s="117" t="s">
+      <c r="F22" s="116" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="116">
+      <c r="A23" s="115">
         <v>1</v>
       </c>
       <c r="B23" s="44" t="s">
@@ -3889,15 +3888,15 @@
         <v>17</v>
       </c>
       <c r="D23" s="44"/>
-      <c r="E23" s="128">
+      <c r="E23" s="127">
         <v>52529</v>
       </c>
-      <c r="F23" s="117" t="s">
+      <c r="F23" s="116" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="116">
+      <c r="A24" s="115">
         <v>1</v>
       </c>
       <c r="B24" s="44" t="s">
@@ -3907,15 +3906,15 @@
         <v>19</v>
       </c>
       <c r="D24" s="44"/>
-      <c r="E24" s="128">
+      <c r="E24" s="127">
         <v>70756</v>
       </c>
-      <c r="F24" s="117" t="s">
+      <c r="F24" s="116" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="116">
+      <c r="A25" s="115">
         <v>1</v>
       </c>
       <c r="B25" s="44" t="s">
@@ -3925,15 +3924,15 @@
         <v>21</v>
       </c>
       <c r="D25" s="44"/>
-      <c r="E25" s="128">
+      <c r="E25" s="127">
         <v>80386</v>
       </c>
-      <c r="F25" s="117" t="s">
+      <c r="F25" s="116" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="116">
+      <c r="A26" s="115">
         <v>1</v>
       </c>
       <c r="B26" s="44" t="s">
@@ -3943,10 +3942,10 @@
         <v>15</v>
       </c>
       <c r="D26" s="44"/>
-      <c r="E26" s="128">
+      <c r="E26" s="127">
         <v>115525</v>
       </c>
-      <c r="F26" s="117" t="s">
+      <c r="F26" s="116" t="s">
         <v>250</v>
       </c>
     </row>
@@ -3955,7 +3954,7 @@
       <c r="B27" s="44"/>
       <c r="C27" s="44"/>
       <c r="D27" s="45"/>
-      <c r="E27" s="129"/>
+      <c r="E27" s="128"/>
       <c r="F27" s="92"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3975,44 +3974,44 @@
       <c r="F29" s="15"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="146" t="s">
+      <c r="A30" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="146" t="s">
+      <c r="C30" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="147" t="s">
+      <c r="D30" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="147"/>
-      <c r="F30" s="147" t="s">
+      <c r="E30" s="144"/>
+      <c r="F30" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="H30" s="152"/>
-      <c r="I30" s="152"/>
-      <c r="J30" s="152"/>
+      <c r="H30" s="145"/>
+      <c r="I30" s="145"/>
+      <c r="J30" s="145"/>
       <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="146"/>
-      <c r="B31" s="146"/>
-      <c r="C31" s="146"/>
-      <c r="D31" s="147"/>
-      <c r="E31" s="147"/>
-      <c r="F31" s="147"/>
+      <c r="A31" s="150"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="150"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144"/>
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="145" t="s">
+      <c r="A32" s="149" t="s">
         <v>214</v>
       </c>
-      <c r="B32" s="145"/>
-      <c r="C32" s="145"/>
-      <c r="D32" s="145"/>
+      <c r="B32" s="149"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="149"/>
       <c r="J32" s="7"/>
       <c r="K32" s="3"/>
     </row>
@@ -4027,13 +4026,13 @@
         <v>257</v>
       </c>
       <c r="D33" s="11"/>
-      <c r="E33" s="130">
+      <c r="E33" s="129">
         <v>263577</v>
       </c>
-      <c r="F33" s="119">
+      <c r="F33" s="118">
         <v>28194</v>
       </c>
-      <c r="G33" s="153" t="s">
+      <c r="G33" s="146" t="s">
         <v>90</v>
       </c>
     </row>
@@ -4048,14 +4047,14 @@
         <v>22</v>
       </c>
       <c r="D34" s="11"/>
-      <c r="E34" s="130">
+      <c r="E34" s="129">
         <v>263577</v>
       </c>
-      <c r="F34" s="119">
+      <c r="F34" s="118">
         <f>E34-(E34*(4/5))</f>
         <v>52715.399999999994</v>
       </c>
-      <c r="G34" s="153"/>
+      <c r="G34" s="146"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
@@ -4068,14 +4067,14 @@
         <v>24</v>
       </c>
       <c r="D35" s="11"/>
-      <c r="E35" s="130">
+      <c r="E35" s="129">
         <v>891716</v>
       </c>
-      <c r="F35" s="119">
+      <c r="F35" s="118">
         <f t="shared" ref="F35:F36" si="0">E35-(E35*(4/5))</f>
         <v>178343.19999999995</v>
       </c>
-      <c r="G35" s="153"/>
+      <c r="G35" s="146"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
@@ -4088,14 +4087,14 @@
         <v>26</v>
       </c>
       <c r="D36" s="35"/>
-      <c r="E36" s="130">
+      <c r="E36" s="129">
         <v>523226</v>
       </c>
-      <c r="F36" s="119">
+      <c r="F36" s="118">
         <f t="shared" si="0"/>
         <v>104645.19999999995</v>
       </c>
-      <c r="G36" s="153"/>
+      <c r="G36" s="146"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
@@ -4103,7 +4102,7 @@
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="91"/>
-      <c r="F37" s="118"/>
+      <c r="F37" s="117"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D38" s="7"/>
@@ -4115,38 +4114,38 @@
       <c r="D40" s="7"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="146" t="s">
+      <c r="A41" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D41" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E41" s="147"/>
-      <c r="F41" s="147" t="s">
+      <c r="E41" s="144"/>
+      <c r="F41" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="146"/>
-      <c r="B42" s="146"/>
-      <c r="C42" s="146"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
+      <c r="A42" s="150"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="144"/>
+      <c r="E42" s="144"/>
+      <c r="F42" s="144"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="145" t="s">
+      <c r="A43" s="149" t="s">
         <v>218</v>
       </c>
-      <c r="B43" s="145"/>
-      <c r="C43" s="145"/>
-      <c r="D43" s="145"/>
+      <c r="B43" s="149"/>
+      <c r="C43" s="149"/>
+      <c r="D43" s="149"/>
       <c r="E43" s="7"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -4160,14 +4159,14 @@
         <v>120</v>
       </c>
       <c r="D44" s="68"/>
-      <c r="E44" s="131">
+      <c r="E44" s="130">
         <v>12396</v>
       </c>
-      <c r="F44" s="120">
+      <c r="F44" s="119">
         <f>E44/2</f>
         <v>6198</v>
       </c>
-      <c r="G44" s="154" t="s">
+      <c r="G44" s="147" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4182,14 +4181,14 @@
         <v>122</v>
       </c>
       <c r="D45" s="68"/>
-      <c r="E45" s="131">
+      <c r="E45" s="130">
         <v>13563</v>
       </c>
-      <c r="F45" s="120">
+      <c r="F45" s="119">
         <f t="shared" ref="F45:F49" si="1">E45/2</f>
         <v>6781.5</v>
       </c>
-      <c r="G45" s="154"/>
+      <c r="G45" s="147"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="87">
@@ -4202,14 +4201,14 @@
         <v>95</v>
       </c>
       <c r="D46" s="68"/>
-      <c r="E46" s="131">
+      <c r="E46" s="130">
         <v>16885</v>
       </c>
-      <c r="F46" s="120">
+      <c r="F46" s="119">
         <f t="shared" si="1"/>
         <v>8442.5</v>
       </c>
-      <c r="G46" s="154"/>
+      <c r="G46" s="147"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="87">
@@ -4222,14 +4221,14 @@
         <v>96</v>
       </c>
       <c r="D47" s="68"/>
-      <c r="E47" s="131">
+      <c r="E47" s="130">
         <v>24410</v>
       </c>
-      <c r="F47" s="120">
+      <c r="F47" s="119">
         <f t="shared" si="1"/>
         <v>12205</v>
       </c>
-      <c r="G47" s="154"/>
+      <c r="G47" s="147"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="87">
@@ -4242,14 +4241,14 @@
         <v>98</v>
       </c>
       <c r="D48" s="68"/>
-      <c r="E48" s="131">
+      <c r="E48" s="130">
         <v>25288</v>
       </c>
-      <c r="F48" s="120">
+      <c r="F48" s="119">
         <f t="shared" si="1"/>
         <v>12644</v>
       </c>
-      <c r="G48" s="154"/>
+      <c r="G48" s="147"/>
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49" s="87">
@@ -4262,14 +4261,13 @@
         <v>29</v>
       </c>
       <c r="D49" s="68"/>
-      <c r="E49" s="131">
+      <c r="E49" s="130">
         <v>163520</v>
       </c>
-      <c r="F49" s="120">
-        <f t="shared" si="1"/>
-        <v>81760</v>
-      </c>
-      <c r="G49" s="154"/>
+      <c r="F49" s="119">
+        <v>33104</v>
+      </c>
+      <c r="G49" s="147"/>
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50" s="87"/>
@@ -4278,39 +4276,39 @@
       <c r="D50" s="88"/>
       <c r="E50" s="89"/>
       <c r="F50" s="90"/>
-      <c r="G50" s="154"/>
+      <c r="G50" s="147"/>
     </row>
     <row r="51" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="G51" s="154"/>
+      <c r="G51" s="147"/>
     </row>
     <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="D52" s="9"/>
     </row>
     <row r="53" spans="1:40" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" s="146" t="s">
+      <c r="A53" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="146" t="s">
+      <c r="C53" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="147" t="s">
+      <c r="D53" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="147"/>
-      <c r="F53" s="147" t="s">
+      <c r="E53" s="144"/>
+      <c r="F53" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:40" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="146"/>
-      <c r="B54" s="146"/>
-      <c r="C54" s="146"/>
-      <c r="D54" s="147"/>
-      <c r="E54" s="147"/>
-      <c r="F54" s="147"/>
+      <c r="A54" s="150"/>
+      <c r="B54" s="150"/>
+      <c r="C54" s="150"/>
+      <c r="D54" s="144"/>
+      <c r="E54" s="144"/>
+      <c r="F54" s="144"/>
       <c r="G54"/>
       <c r="H54"/>
       <c r="I54"/>
@@ -4347,12 +4345,12 @@
       <c r="AN54"/>
     </row>
     <row r="55" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="145" t="s">
+      <c r="A55" s="149" t="s">
         <v>219</v>
       </c>
-      <c r="B55" s="145"/>
-      <c r="C55" s="145"/>
-      <c r="D55" s="145"/>
+      <c r="B55" s="149"/>
+      <c r="C55" s="149"/>
+      <c r="D55" s="149"/>
     </row>
     <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56" s="50">
@@ -4365,10 +4363,10 @@
         <v>39</v>
       </c>
       <c r="D56" s="46"/>
-      <c r="E56" s="132">
+      <c r="E56" s="131">
         <v>9191</v>
       </c>
-      <c r="F56" s="121">
+      <c r="F56" s="120">
         <f>E56/2</f>
         <v>4595.5</v>
       </c>
@@ -4384,14 +4382,14 @@
         <v>35</v>
       </c>
       <c r="D57" s="46"/>
-      <c r="E57" s="133">
+      <c r="E57" s="132">
         <v>17813</v>
       </c>
-      <c r="F57" s="121">
+      <c r="F57" s="120">
         <f t="shared" ref="F57:F60" si="2">E57/2</f>
         <v>8906.5</v>
       </c>
-      <c r="G57" s="155" t="s">
+      <c r="G57" s="148" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4406,14 +4404,14 @@
         <v>33</v>
       </c>
       <c r="D58" s="46"/>
-      <c r="E58" s="134">
+      <c r="E58" s="133">
         <v>20940</v>
       </c>
-      <c r="F58" s="121">
+      <c r="F58" s="120">
         <f t="shared" si="2"/>
         <v>10470</v>
       </c>
-      <c r="G58" s="155"/>
+      <c r="G58" s="148"/>
     </row>
     <row r="59" spans="1:40" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="50">
@@ -4426,14 +4424,14 @@
         <v>37</v>
       </c>
       <c r="D59" s="46"/>
-      <c r="E59" s="133">
+      <c r="E59" s="132">
         <v>22437</v>
       </c>
-      <c r="F59" s="121">
+      <c r="F59" s="120">
         <f t="shared" si="2"/>
         <v>11218.5</v>
       </c>
-      <c r="G59" s="155"/>
+      <c r="G59" s="148"/>
     </row>
     <row r="60" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="34">
@@ -4446,14 +4444,14 @@
         <v>41</v>
       </c>
       <c r="D60" s="46"/>
-      <c r="E60" s="133">
+      <c r="E60" s="132">
         <v>49232</v>
       </c>
-      <c r="F60" s="121">
+      <c r="F60" s="120">
         <f t="shared" si="2"/>
         <v>24616</v>
       </c>
-      <c r="G60" s="155"/>
+      <c r="G60" s="148"/>
       <c r="H60"/>
       <c r="I60"/>
       <c r="J60"/>
@@ -4495,7 +4493,7 @@
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="48"/>
-      <c r="G61" s="155"/>
+      <c r="G61" s="148"/>
       <c r="H61"/>
       <c r="I61"/>
       <c r="J61"/>
@@ -4531,45 +4529,45 @@
       <c r="AN61"/>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="G62" s="155"/>
+      <c r="G62" s="148"/>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="D63" s="7"/>
     </row>
     <row r="64" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A64" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" s="146" t="s">
+      <c r="A64" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="146" t="s">
+      <c r="C64" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D64" s="147" t="s">
+      <c r="D64" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E64" s="147"/>
-      <c r="F64" s="147" t="s">
+      <c r="E64" s="144"/>
+      <c r="F64" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="146"/>
-      <c r="B65" s="146"/>
-      <c r="C65" s="146"/>
-      <c r="D65" s="147"/>
-      <c r="E65" s="147"/>
-      <c r="F65" s="147"/>
+      <c r="A65" s="150"/>
+      <c r="B65" s="150"/>
+      <c r="C65" s="150"/>
+      <c r="D65" s="144"/>
+      <c r="E65" s="144"/>
+      <c r="F65" s="144"/>
     </row>
     <row r="66" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="145" t="s">
+      <c r="A66" s="149" t="s">
         <v>223</v>
       </c>
-      <c r="B66" s="145"/>
-      <c r="C66" s="145"/>
-      <c r="D66" s="145"/>
-      <c r="G66" s="154" t="s">
+      <c r="B66" s="149"/>
+      <c r="C66" s="149"/>
+      <c r="D66" s="149"/>
+      <c r="G66" s="147" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4584,14 +4582,14 @@
         <v>44</v>
       </c>
       <c r="D67" s="52"/>
-      <c r="E67" s="135">
+      <c r="E67" s="134">
         <v>16960</v>
       </c>
-      <c r="F67" s="122">
+      <c r="F67" s="121">
         <f>E67/2</f>
         <v>8480</v>
       </c>
-      <c r="G67" s="154"/>
+      <c r="G67" s="147"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="46">
@@ -4604,14 +4602,14 @@
         <v>46</v>
       </c>
       <c r="D68" s="52"/>
-      <c r="E68" s="135">
+      <c r="E68" s="134">
         <v>26056</v>
       </c>
-      <c r="F68" s="122">
+      <c r="F68" s="121">
         <f t="shared" ref="F68:F69" si="3">E68/2</f>
         <v>13028</v>
       </c>
-      <c r="G68" s="154"/>
+      <c r="G68" s="147"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="46">
@@ -4624,14 +4622,14 @@
         <v>48</v>
       </c>
       <c r="D69" s="52"/>
-      <c r="E69" s="135">
+      <c r="E69" s="134">
         <v>28141</v>
       </c>
-      <c r="F69" s="122">
+      <c r="F69" s="121">
         <f t="shared" si="3"/>
         <v>14070.5</v>
       </c>
-      <c r="G69" s="154"/>
+      <c r="G69" s="147"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="46">
@@ -4644,59 +4642,59 @@
         <v>50</v>
       </c>
       <c r="D70" s="52"/>
-      <c r="E70" s="135">
+      <c r="E70" s="134">
         <v>47546</v>
       </c>
-      <c r="F70" s="122">
+      <c r="F70" s="121">
         <f>E70/2</f>
         <v>23773</v>
       </c>
-      <c r="G70" s="154"/>
+      <c r="G70" s="147"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B71" s="29"/>
       <c r="C71" s="31"/>
       <c r="D71" s="7"/>
-      <c r="E71" s="136"/>
+      <c r="E71" s="135"/>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B72" s="146" t="s">
+      <c r="A72" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="146" t="s">
+      <c r="C72" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D72" s="147" t="s">
+      <c r="D72" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="147"/>
-      <c r="F72" s="147" t="s">
+      <c r="E72" s="144"/>
+      <c r="F72" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="146"/>
-      <c r="B73" s="146"/>
-      <c r="C73" s="146"/>
-      <c r="D73" s="147"/>
-      <c r="E73" s="147"/>
-      <c r="F73" s="147"/>
-      <c r="G73" s="153" t="s">
+      <c r="A73" s="150"/>
+      <c r="B73" s="150"/>
+      <c r="C73" s="150"/>
+      <c r="D73" s="144"/>
+      <c r="E73" s="144"/>
+      <c r="F73" s="144"/>
+      <c r="G73" s="146" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="145" t="s">
+      <c r="A74" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B74" s="145"/>
-      <c r="C74" s="145"/>
-      <c r="D74" s="145"/>
-      <c r="G74" s="153"/>
+      <c r="B74" s="149"/>
+      <c r="C74" s="149"/>
+      <c r="D74" s="149"/>
+      <c r="G74" s="146"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="33">
@@ -4717,7 +4715,7 @@
       <c r="F75" s="83">
         <v>1232</v>
       </c>
-      <c r="G75" s="153"/>
+      <c r="G75" s="146"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="33">
@@ -4738,7 +4736,7 @@
       <c r="F76" s="83">
         <v>720</v>
       </c>
-      <c r="G76" s="153"/>
+      <c r="G76" s="146"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D77"/>
@@ -4752,7 +4750,7 @@
     </row>
     <row r="79" spans="1:7" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.25">
       <c r="B79"/>
-      <c r="C79" s="107" t="s">
+      <c r="C79" s="106" t="s">
         <v>54</v>
       </c>
       <c r="D79"/>
@@ -4810,7 +4808,7 @@
       <c r="F89"/>
     </row>
     <row r="90" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C90" s="107" t="s">
+      <c r="C90" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D90"/>
@@ -4855,15 +4853,31 @@
     <row r="102" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G33:G36"/>
-    <mergeCell ref="G73:G76"/>
-    <mergeCell ref="G66:G70"/>
-    <mergeCell ref="G44:G51"/>
-    <mergeCell ref="G57:G62"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:E73"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:E19"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:E42"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:E31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="F53:F54"/>
@@ -4880,31 +4894,15 @@
     <mergeCell ref="C53:C54"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:E19"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:E42"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:E31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G33:G36"/>
+    <mergeCell ref="G73:G76"/>
+    <mergeCell ref="G66:G70"/>
+    <mergeCell ref="G44:G51"/>
+    <mergeCell ref="G57:G62"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4930,126 +4928,126 @@
   </cols>
   <sheetData>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="158" t="s">
+      <c r="B9" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="158"/>
-      <c r="D9" s="158"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="155"/>
       <c r="E9" s="24"/>
     </row>
     <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="158"/>
-      <c r="C10" s="158"/>
-      <c r="D10" s="158"/>
+      <c r="B10" s="155"/>
+      <c r="C10" s="155"/>
+      <c r="D10" s="155"/>
       <c r="E10" s="24"/>
     </row>
     <row r="11" spans="1:6" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
-      <c r="D11" s="158"/>
+      <c r="B11" s="155"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="155"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="146" t="s">
+      <c r="A13" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="147" t="s">
+      <c r="D13" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="147" t="s">
+      <c r="E13" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="146"/>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="147"/>
+      <c r="A14" s="150"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="149" t="s">
+      <c r="A15" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="149"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="149"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
       <c r="E15" s="26"/>
     </row>
     <row r="16" spans="1:6" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="124">
-        <v>1</v>
-      </c>
-      <c r="B16" s="124" t="s">
+      <c r="A16" s="123">
+        <v>1</v>
+      </c>
+      <c r="B16" s="123" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="124" t="s">
+      <c r="C16" s="123" t="s">
         <v>251</v>
       </c>
-      <c r="D16" s="140"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="159" t="s">
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="156" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="156" t="s">
+      <c r="A17" s="157" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="157"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="141">
+      <c r="B17" s="158"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140">
         <v>86000</v>
       </c>
-      <c r="F17" s="159"/>
+      <c r="F17" s="156"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="137"/>
-      <c r="B18" s="137"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="139"/>
+      <c r="A18" s="136"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="138"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="146" t="s">
+      <c r="A20" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="146" t="s">
+      <c r="C20" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="147" t="s">
+      <c r="D20" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="147" t="s">
+      <c r="E20" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="146"/>
-      <c r="B21" s="146"/>
-      <c r="C21" s="146"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="147"/>
+      <c r="A21" s="150"/>
+      <c r="B21" s="150"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="144"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="145" t="s">
+      <c r="A22" s="149" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="145"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="145"/>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5067,7 +5065,7 @@
         <f>30941/2</f>
         <v>15470.5</v>
       </c>
-      <c r="G23" s="123"/>
+      <c r="G23" s="122"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="74">
@@ -5096,7 +5094,7 @@
         <v>69</v>
       </c>
       <c r="D25" s="52"/>
-      <c r="E25" s="122">
+      <c r="E25" s="121">
         <f>62797/2</f>
         <v>31398.5</v>
       </c>
@@ -5168,36 +5166,36 @@
       <c r="E31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="146" t="s">
+      <c r="A32" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="146" t="s">
+      <c r="C32" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="147" t="s">
+      <c r="D32" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="147" t="s">
+      <c r="E32" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="146"/>
-      <c r="B33" s="146"/>
-      <c r="C33" s="146"/>
-      <c r="D33" s="147"/>
-      <c r="E33" s="147"/>
+      <c r="A33" s="150"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="150"/>
+      <c r="D33" s="144"/>
+      <c r="E33" s="144"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="145" t="s">
+      <c r="A34" s="149" t="s">
         <v>220</v>
       </c>
-      <c r="B34" s="145"/>
-      <c r="C34" s="145"/>
-      <c r="D34" s="145"/>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="149"/>
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5211,7 +5209,7 @@
         <v>257</v>
       </c>
       <c r="D35" s="25"/>
-      <c r="E35" s="119">
+      <c r="E35" s="118">
         <v>28194</v>
       </c>
     </row>
@@ -5229,7 +5227,7 @@
       <c r="E36" s="78">
         <v>52715.399999999994</v>
       </c>
-      <c r="F36" s="153" t="s">
+      <c r="F36" s="146" t="s">
         <v>90</v>
       </c>
     </row>
@@ -5247,7 +5245,7 @@
       <c r="E37" s="80">
         <v>178343.19999999995</v>
       </c>
-      <c r="F37" s="153"/>
+      <c r="F37" s="146"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="74">
@@ -5263,7 +5261,7 @@
       <c r="E38" s="78">
         <v>104645.19999999995</v>
       </c>
-      <c r="F38" s="153"/>
+      <c r="F38" s="146"/>
     </row>
     <row r="39" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="74"/>
@@ -5277,38 +5275,38 @@
       <c r="E40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="146" t="s">
+      <c r="A41" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D41" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E41" s="147" t="s">
+      <c r="E41" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="146"/>
-      <c r="B42" s="146"/>
-      <c r="C42" s="146"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
+      <c r="A42" s="150"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="144"/>
+      <c r="E42" s="144"/>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="145" t="s">
+      <c r="A43" s="149" t="s">
         <v>221</v>
       </c>
-      <c r="B43" s="145"/>
-      <c r="C43" s="145"/>
-      <c r="D43" s="145"/>
+      <c r="B43" s="149"/>
+      <c r="C43" s="149"/>
+      <c r="D43" s="149"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="154" t="s">
+      <c r="F43" s="147" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5326,7 +5324,7 @@
       <c r="E44" s="89">
         <v>6198</v>
       </c>
-      <c r="F44" s="154"/>
+      <c r="F44" s="147"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="87">
@@ -5342,7 +5340,7 @@
       <c r="E45" s="89">
         <v>6781.5</v>
       </c>
-      <c r="F45" s="154"/>
+      <c r="F45" s="147"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="87">
@@ -5358,7 +5356,7 @@
       <c r="E46" s="89">
         <v>8442.5</v>
       </c>
-      <c r="F46" s="154"/>
+      <c r="F46" s="147"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="87">
@@ -5374,7 +5372,7 @@
       <c r="E47" s="89">
         <v>12205</v>
       </c>
-      <c r="F47" s="154"/>
+      <c r="F47" s="147"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="87">
@@ -5390,7 +5388,7 @@
       <c r="E48" s="89">
         <v>12644</v>
       </c>
-      <c r="F48" s="154"/>
+      <c r="F48" s="147"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="87">
@@ -5403,10 +5401,10 @@
         <v>29</v>
       </c>
       <c r="D49" s="68"/>
-      <c r="E49" s="89">
-        <v>81760</v>
-      </c>
-      <c r="F49" s="154"/>
+      <c r="E49" s="119">
+        <v>33104</v>
+      </c>
+      <c r="F49" s="147"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="48"/>
@@ -5414,7 +5412,7 @@
       <c r="C50" s="48"/>
       <c r="D50" s="82"/>
       <c r="E50" s="47"/>
-      <c r="F50" s="154"/>
+      <c r="F50" s="147"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D51" s="7"/>
@@ -5423,39 +5421,39 @@
       <c r="D52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" s="146" t="s">
+      <c r="A53" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="146" t="s">
+      <c r="C53" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D53" s="147" t="s">
+      <c r="D53" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E53" s="147" t="s">
+      <c r="E53" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="146"/>
-      <c r="B54" s="146"/>
-      <c r="C54" s="146"/>
-      <c r="D54" s="147"/>
-      <c r="E54" s="147"/>
+      <c r="A54" s="150"/>
+      <c r="B54" s="150"/>
+      <c r="C54" s="150"/>
+      <c r="D54" s="144"/>
+      <c r="E54" s="144"/>
       <c r="G54"/>
       <c r="H54"/>
       <c r="I54"/>
     </row>
     <row r="55" spans="1:9" s="1" customFormat="1" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="145" t="s">
+      <c r="A55" s="149" t="s">
         <v>150</v>
       </c>
-      <c r="B55" s="145"/>
-      <c r="C55" s="145"/>
-      <c r="D55" s="145"/>
+      <c r="B55" s="149"/>
+      <c r="C55" s="149"/>
+      <c r="D55" s="149"/>
       <c r="E55" s="3"/>
       <c r="G55"/>
       <c r="H55"/>
@@ -5475,7 +5473,7 @@
       <c r="E56" s="86">
         <v>4595.5</v>
       </c>
-      <c r="F56" s="155" t="s">
+      <c r="F56" s="148" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5493,7 +5491,7 @@
       <c r="E57" s="85">
         <v>8906.5</v>
       </c>
-      <c r="F57" s="155"/>
+      <c r="F57" s="148"/>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="34">
@@ -5509,7 +5507,7 @@
       <c r="E58" s="84">
         <v>10470</v>
       </c>
-      <c r="F58" s="155"/>
+      <c r="F58" s="148"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="50">
@@ -5525,7 +5523,7 @@
       <c r="E59" s="85">
         <v>11218.5</v>
       </c>
-      <c r="F59" s="155"/>
+      <c r="F59" s="148"/>
     </row>
     <row r="60" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="34">
@@ -5541,7 +5539,7 @@
       <c r="E60" s="85">
         <v>24616</v>
       </c>
-      <c r="F60" s="155"/>
+      <c r="F60" s="148"/>
       <c r="G60"/>
       <c r="H60"/>
       <c r="I60"/>
@@ -5552,44 +5550,44 @@
       <c r="C61" s="71"/>
       <c r="D61" s="33"/>
       <c r="E61" s="33"/>
-      <c r="F61" s="155"/>
+      <c r="F61" s="148"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D62" s="3"/>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B63" s="146" t="s">
+      <c r="A63" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C63" s="146" t="s">
+      <c r="C63" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D63" s="147" t="s">
+      <c r="D63" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E63" s="147" t="s">
+      <c r="E63" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="146"/>
-      <c r="B64" s="146"/>
-      <c r="C64" s="146"/>
-      <c r="D64" s="147"/>
-      <c r="E64" s="147"/>
+      <c r="A64" s="150"/>
+      <c r="B64" s="150"/>
+      <c r="C64" s="150"/>
+      <c r="D64" s="144"/>
+      <c r="E64" s="144"/>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="145" t="s">
+      <c r="A65" s="149" t="s">
         <v>222</v>
       </c>
-      <c r="B65" s="145"/>
-      <c r="C65" s="145"/>
-      <c r="D65" s="145"/>
+      <c r="B65" s="149"/>
+      <c r="C65" s="149"/>
+      <c r="D65" s="149"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="153" t="s">
+      <c r="F65" s="146" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5607,7 +5605,7 @@
       <c r="E66" s="73">
         <v>8480</v>
       </c>
-      <c r="F66" s="153"/>
+      <c r="F66" s="146"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="46">
@@ -5623,7 +5621,7 @@
       <c r="E67" s="73">
         <v>13028</v>
       </c>
-      <c r="F67" s="153"/>
+      <c r="F67" s="146"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="46">
@@ -5639,7 +5637,7 @@
       <c r="E68" s="73">
         <v>14070.5</v>
       </c>
-      <c r="F68" s="153"/>
+      <c r="F68" s="146"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="46">
@@ -5655,44 +5653,44 @@
       <c r="E69" s="73">
         <v>23773</v>
       </c>
-      <c r="F69" s="153"/>
+      <c r="F69" s="146"/>
     </row>
     <row r="71" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B71" s="146" t="s">
+      <c r="A71" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="146" t="s">
+      <c r="C71" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D71" s="147" t="s">
+      <c r="D71" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E71" s="147" t="s">
+      <c r="E71" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="146"/>
-      <c r="B72" s="146"/>
-      <c r="C72" s="146"/>
-      <c r="D72" s="147"/>
-      <c r="E72" s="147"/>
-      <c r="F72" s="153" t="s">
+      <c r="A72" s="150"/>
+      <c r="B72" s="150"/>
+      <c r="C72" s="150"/>
+      <c r="D72" s="144"/>
+      <c r="E72" s="144"/>
+      <c r="F72" s="146" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="145" t="s">
+      <c r="A73" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B73" s="145"/>
-      <c r="C73" s="145"/>
-      <c r="D73" s="145"/>
+      <c r="B73" s="149"/>
+      <c r="C73" s="149"/>
+      <c r="D73" s="149"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="153"/>
+      <c r="F73" s="146"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
@@ -5710,7 +5708,7 @@
       <c r="E74" s="14">
         <v>1232</v>
       </c>
-      <c r="F74" s="153"/>
+      <c r="F74" s="146"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
@@ -5728,7 +5726,7 @@
       <c r="E75" s="14">
         <v>720</v>
       </c>
-      <c r="F75" s="153"/>
+      <c r="F75" s="146"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D76"/>
@@ -5736,7 +5734,7 @@
     </row>
     <row r="77" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
-      <c r="C77" s="107" t="s">
+      <c r="C77" s="106" t="s">
         <v>54</v>
       </c>
       <c r="D77"/>
@@ -5788,7 +5786,7 @@
       <c r="E87"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C88" s="107" t="s">
+      <c r="C88" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D88"/>
@@ -5864,6 +5862,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="F36:F38"/>
+    <mergeCell ref="F65:F69"/>
+    <mergeCell ref="F43:F50"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="B9:D11"/>
     <mergeCell ref="F56:F61"/>
     <mergeCell ref="E20:E21"/>
@@ -5880,40 +5912,6 @@
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="B53:B54"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="F36:F38"/>
-    <mergeCell ref="F65:F69"/>
-    <mergeCell ref="F43:F50"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="F72:F75"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A53:A54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5937,65 +5935,65 @@
   </cols>
   <sheetData>
     <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="159" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="165"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="161"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="166"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="167"/>
+      <c r="B8" s="162"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="163"/>
       <c r="E8" s="24"/>
     </row>
     <row r="9" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="166"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="167"/>
+      <c r="B9" s="162"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="163"/>
       <c r="E9" s="24"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="168"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="170"/>
+      <c r="B10" s="164"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="166"/>
       <c r="F10" s="6">
         <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="146" t="s">
+      <c r="A12" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="147" t="s">
+      <c r="D12" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="147" t="s">
+      <c r="E12" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="146"/>
-      <c r="B13" s="146"/>
-      <c r="C13" s="146"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
+      <c r="A13" s="150"/>
+      <c r="B13" s="150"/>
+      <c r="C13" s="150"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="149" t="s">
+      <c r="A14" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
+      <c r="B14" s="154"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
       <c r="E14" s="26"/>
-      <c r="F14" s="159" t="s">
+      <c r="F14" s="156" t="s">
         <v>254</v>
       </c>
     </row>
@@ -6011,61 +6009,61 @@
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="14"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="159"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="156"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="161" t="s">
+      <c r="A16" s="167" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="162"/>
+      <c r="B16" s="168"/>
       <c r="C16" s="17"/>
       <c r="D16" s="18"/>
       <c r="E16" s="14">
         <v>95000</v>
       </c>
-      <c r="F16" s="159"/>
-      <c r="G16" s="159"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="156"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D17" s="8"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="146" t="s">
+      <c r="A18" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="146" t="s">
+      <c r="C18" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="147" t="s">
+      <c r="D18" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="147" t="s">
+      <c r="E18" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="146"/>
-      <c r="B19" s="146"/>
-      <c r="C19" s="146"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="147"/>
+      <c r="A19" s="150"/>
+      <c r="B19" s="150"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="144"/>
+      <c r="E19" s="144"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="145" t="s">
+      <c r="A20" s="149" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="145"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="145"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="116">
+      <c r="A21" s="115">
         <v>1</v>
       </c>
       <c r="B21" s="44" t="s">
@@ -6075,13 +6073,13 @@
         <v>163</v>
       </c>
       <c r="D21" s="44"/>
-      <c r="E21" s="117" t="s">
+      <c r="E21" s="116" t="s">
         <v>245</v>
       </c>
       <c r="F21" s="30"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="116">
+      <c r="A22" s="115">
         <v>1</v>
       </c>
       <c r="B22" s="44" t="s">
@@ -6091,12 +6089,12 @@
         <v>13</v>
       </c>
       <c r="D22" s="44"/>
-      <c r="E22" s="117" t="s">
+      <c r="E22" s="116" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="116">
+      <c r="A23" s="115">
         <v>1</v>
       </c>
       <c r="B23" s="44" t="s">
@@ -6106,13 +6104,13 @@
         <v>17</v>
       </c>
       <c r="D23" s="44"/>
-      <c r="E23" s="117" t="s">
+      <c r="E23" s="116" t="s">
         <v>247</v>
       </c>
       <c r="F23" s="31"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="116">
+      <c r="A24" s="115">
         <v>1</v>
       </c>
       <c r="B24" s="44" t="s">
@@ -6122,13 +6120,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="44"/>
-      <c r="E24" s="117" t="s">
+      <c r="E24" s="116" t="s">
         <v>248</v>
       </c>
       <c r="F24" s="30"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="116">
+      <c r="A25" s="115">
         <v>1</v>
       </c>
       <c r="B25" s="44" t="s">
@@ -6138,13 +6136,13 @@
         <v>21</v>
       </c>
       <c r="D25" s="44"/>
-      <c r="E25" s="117" t="s">
+      <c r="E25" s="116" t="s">
         <v>249</v>
       </c>
       <c r="F25" s="31"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="116">
+      <c r="A26" s="115">
         <v>1</v>
       </c>
       <c r="B26" s="44" t="s">
@@ -6154,7 +6152,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="44"/>
-      <c r="E26" s="117" t="s">
+      <c r="E26" s="116" t="s">
         <v>250</v>
       </c>
       <c r="F26" s="31"/>
@@ -6171,36 +6169,36 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="146" t="s">
+      <c r="A29" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="146" t="s">
+      <c r="C29" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="147" t="s">
+      <c r="D29" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="147" t="s">
+      <c r="E29" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="146"/>
-      <c r="B30" s="146"/>
-      <c r="C30" s="146"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="147"/>
+      <c r="A30" s="150"/>
+      <c r="B30" s="150"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="144"/>
+      <c r="E30" s="144"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="145" t="s">
+      <c r="A31" s="149" t="s">
         <v>88</v>
       </c>
-      <c r="B31" s="145"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="145"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="149"/>
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -6214,7 +6212,7 @@
         <v>257</v>
       </c>
       <c r="D32" s="25"/>
-      <c r="E32" s="119">
+      <c r="E32" s="118">
         <v>28194</v>
       </c>
     </row>
@@ -6232,7 +6230,7 @@
       <c r="E33" s="98">
         <v>52715.399999999994</v>
       </c>
-      <c r="F33" s="153" t="s">
+      <c r="F33" s="146" t="s">
         <v>90</v>
       </c>
     </row>
@@ -6250,7 +6248,7 @@
       <c r="E34" s="98">
         <v>178343.19999999995</v>
       </c>
-      <c r="F34" s="153"/>
+      <c r="F34" s="146"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="46">
@@ -6282,38 +6280,38 @@
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="146" t="s">
+      <c r="A39" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="146" t="s">
+      <c r="C39" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="147" t="s">
+      <c r="D39" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E39" s="147" t="s">
+      <c r="E39" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="146"/>
-      <c r="B40" s="146"/>
-      <c r="C40" s="146"/>
-      <c r="D40" s="147"/>
-      <c r="E40" s="147"/>
+      <c r="A40" s="150"/>
+      <c r="B40" s="150"/>
+      <c r="C40" s="150"/>
+      <c r="D40" s="144"/>
+      <c r="E40" s="144"/>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="145" t="s">
+      <c r="A41" s="149" t="s">
         <v>224</v>
       </c>
-      <c r="B41" s="145"/>
-      <c r="C41" s="145"/>
-      <c r="D41" s="145"/>
+      <c r="B41" s="149"/>
+      <c r="C41" s="149"/>
+      <c r="D41" s="149"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="154" t="s">
+      <c r="F41" s="147" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6331,7 +6329,7 @@
       <c r="E42" s="89">
         <v>6198</v>
       </c>
-      <c r="F42" s="154"/>
+      <c r="F42" s="147"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="87">
@@ -6347,7 +6345,7 @@
       <c r="E43" s="89">
         <v>6781.5</v>
       </c>
-      <c r="F43" s="154"/>
+      <c r="F43" s="147"/>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="87">
@@ -6363,7 +6361,7 @@
       <c r="E44" s="89">
         <v>8442.5</v>
       </c>
-      <c r="F44" s="154"/>
+      <c r="F44" s="147"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="87">
@@ -6379,7 +6377,7 @@
       <c r="E45" s="89">
         <v>12205</v>
       </c>
-      <c r="F45" s="154"/>
+      <c r="F45" s="147"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="87">
@@ -6395,7 +6393,7 @@
       <c r="E46" s="89">
         <v>12644</v>
       </c>
-      <c r="F46" s="154"/>
+      <c r="F46" s="147"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="87">
@@ -6408,10 +6406,10 @@
         <v>29</v>
       </c>
       <c r="D47" s="68"/>
-      <c r="E47" s="89">
-        <v>81760</v>
-      </c>
-      <c r="F47" s="154"/>
+      <c r="E47" s="119">
+        <v>33104</v>
+      </c>
+      <c r="F47" s="147"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="48"/>
@@ -6419,42 +6417,42 @@
       <c r="C48" s="48"/>
       <c r="D48" s="82"/>
       <c r="E48" s="47"/>
-      <c r="F48" s="154"/>
+      <c r="F48" s="147"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B50" s="146" t="s">
+      <c r="A50" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="146" t="s">
+      <c r="C50" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D50" s="147" t="s">
+      <c r="D50" s="144" t="s">
         <v>4</v>
       </c>
       <c r="E50" s="51"/>
     </row>
     <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="146"/>
-      <c r="B51" s="146"/>
-      <c r="C51" s="146"/>
-      <c r="D51" s="147"/>
+      <c r="A51" s="150"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="150"/>
+      <c r="D51" s="144"/>
       <c r="E51" s="51"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="145" t="s">
+      <c r="A52" s="149" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="145"/>
-      <c r="C52" s="145"/>
-      <c r="D52" s="145"/>
+      <c r="B52" s="149"/>
+      <c r="C52" s="149"/>
+      <c r="D52" s="149"/>
       <c r="E52" s="65"/>
-      <c r="F52" s="160" t="s">
+      <c r="F52" s="169" t="s">
         <v>80</v>
       </c>
     </row>
@@ -6472,7 +6470,7 @@
       <c r="E53" s="86">
         <v>4595.5</v>
       </c>
-      <c r="F53" s="154"/>
+      <c r="F53" s="147"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="34">
@@ -6488,7 +6486,7 @@
       <c r="E54" s="85">
         <v>8906.5</v>
       </c>
-      <c r="F54" s="154"/>
+      <c r="F54" s="147"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="34">
@@ -6504,7 +6502,7 @@
       <c r="E55" s="84">
         <v>10470</v>
       </c>
-      <c r="F55" s="154"/>
+      <c r="F55" s="147"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="50">
@@ -6520,7 +6518,7 @@
       <c r="E56" s="85">
         <v>11218.5</v>
       </c>
-      <c r="F56" s="154"/>
+      <c r="F56" s="147"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="34">
@@ -6536,7 +6534,7 @@
       <c r="E57" s="85">
         <v>24616</v>
       </c>
-      <c r="F57" s="154"/>
+      <c r="F57" s="147"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="71"/>
@@ -6544,7 +6542,7 @@
       <c r="C58" s="71"/>
       <c r="D58" s="33"/>
       <c r="E58" s="33"/>
-      <c r="F58" s="154"/>
+      <c r="F58" s="147"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D59"/>
@@ -6554,38 +6552,38 @@
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61" s="146" t="s">
+      <c r="A61" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="146" t="s">
+      <c r="C61" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D61" s="147" t="s">
+      <c r="D61" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E61" s="147" t="s">
+      <c r="E61" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="146"/>
-      <c r="B62" s="146"/>
-      <c r="C62" s="146"/>
-      <c r="D62" s="147"/>
-      <c r="E62" s="147"/>
+      <c r="A62" s="150"/>
+      <c r="B62" s="150"/>
+      <c r="C62" s="150"/>
+      <c r="D62" s="144"/>
+      <c r="E62" s="144"/>
     </row>
     <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="145" t="s">
+      <c r="A63" s="149" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="145"/>
-      <c r="C63" s="145"/>
-      <c r="D63" s="145"/>
+      <c r="B63" s="149"/>
+      <c r="C63" s="149"/>
+      <c r="D63" s="149"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="154" t="s">
+      <c r="F63" s="147" t="s">
         <v>42</v>
       </c>
     </row>
@@ -6603,7 +6601,7 @@
       <c r="E64" s="73">
         <v>8480</v>
       </c>
-      <c r="F64" s="154"/>
+      <c r="F64" s="147"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="46">
@@ -6619,7 +6617,7 @@
       <c r="E65" s="73">
         <v>13028</v>
       </c>
-      <c r="F65" s="154"/>
+      <c r="F65" s="147"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="46">
@@ -6635,7 +6633,7 @@
       <c r="E66" s="73">
         <v>14070.5</v>
       </c>
-      <c r="F66" s="154"/>
+      <c r="F66" s="147"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="46">
@@ -6651,44 +6649,44 @@
       <c r="E67" s="73">
         <v>23773</v>
       </c>
-      <c r="F67" s="154"/>
+      <c r="F67" s="147"/>
     </row>
     <row r="69" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="146" t="s">
+      <c r="A69" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="146" t="s">
+      <c r="C69" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="147" t="s">
+      <c r="D69" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E69" s="147" t="s">
+      <c r="E69" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="146"/>
-      <c r="B70" s="146"/>
-      <c r="C70" s="146"/>
-      <c r="D70" s="147"/>
-      <c r="E70" s="147"/>
-      <c r="F70" s="153" t="s">
+      <c r="A70" s="150"/>
+      <c r="B70" s="150"/>
+      <c r="C70" s="150"/>
+      <c r="D70" s="144"/>
+      <c r="E70" s="144"/>
+      <c r="F70" s="146" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="145" t="s">
+      <c r="A71" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B71" s="145"/>
-      <c r="C71" s="145"/>
-      <c r="D71" s="145"/>
+      <c r="B71" s="149"/>
+      <c r="C71" s="149"/>
+      <c r="D71" s="149"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="153"/>
+      <c r="F71" s="146"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
@@ -6706,7 +6704,7 @@
       <c r="E72" s="14">
         <v>1232</v>
       </c>
-      <c r="F72" s="153"/>
+      <c r="F72" s="146"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
@@ -6724,14 +6722,14 @@
       <c r="E73" s="14">
         <v>720</v>
       </c>
-      <c r="F73" s="153"/>
+      <c r="F73" s="146"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D74"/>
     </row>
     <row r="75" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
-      <c r="C75" s="107" t="s">
+      <c r="C75" s="106" t="s">
         <v>54</v>
       </c>
       <c r="D75"/>
@@ -6768,7 +6766,7 @@
       <c r="D85"/>
     </row>
     <row r="86" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C86" s="107" t="s">
+      <c r="C86" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D86"/>
@@ -6820,41 +6818,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="B7:D10"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="F63:F67"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F41:F48"/>
     <mergeCell ref="G15:G16"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="F52:F58"/>
@@ -6870,6 +6833,41 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="F63:F67"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="F41:F48"/>
+    <mergeCell ref="B7:D10"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="C29:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6892,64 +6890,64 @@
   </cols>
   <sheetData>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="171" t="s">
+      <c r="B6" s="170" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="173"/>
+      <c r="C6" s="171"/>
+      <c r="D6" s="171"/>
+      <c r="E6" s="172"/>
     </row>
     <row r="7" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="174"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="175"/>
-      <c r="E7" s="176"/>
+      <c r="B7" s="173"/>
+      <c r="C7" s="174"/>
+      <c r="D7" s="174"/>
+      <c r="E7" s="175"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="174"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="176"/>
+      <c r="B8" s="173"/>
+      <c r="C8" s="174"/>
+      <c r="D8" s="174"/>
+      <c r="E8" s="175"/>
     </row>
     <row r="9" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="177"/>
-      <c r="C9" s="178"/>
-      <c r="D9" s="178"/>
-      <c r="E9" s="179"/>
+      <c r="B9" s="176"/>
+      <c r="C9" s="177"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="178"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="146" t="s">
+      <c r="A11" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="147" t="s">
+      <c r="D11" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="147" t="s">
+      <c r="E11" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="146"/>
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
+      <c r="A12" s="150"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="149" t="s">
+      <c r="A13" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="149"/>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
+      <c r="B13" s="154"/>
+      <c r="C13" s="154"/>
+      <c r="D13" s="154"/>
       <c r="E13" s="26"/>
-      <c r="F13" s="159" t="s">
+      <c r="F13" s="156" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="6">
@@ -6968,55 +6966,55 @@
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="67"/>
-      <c r="F14" s="159"/>
+      <c r="F14" s="156"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="161" t="s">
+      <c r="A15" s="167" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="162"/>
+      <c r="B15" s="168"/>
       <c r="C15" s="17"/>
       <c r="D15" s="19"/>
       <c r="E15" s="14">
         <v>98000</v>
       </c>
-      <c r="F15" s="159"/>
+      <c r="F15" s="156"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D16" s="6"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="146" t="s">
+      <c r="A17" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="146" t="s">
+      <c r="C17" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="147" t="s">
+      <c r="D17" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="147" t="s">
+      <c r="E17" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="146"/>
-      <c r="B18" s="146"/>
-      <c r="C18" s="146"/>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
+      <c r="A18" s="150"/>
+      <c r="B18" s="150"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="144"/>
+      <c r="E18" s="144"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="145" t="s">
+      <c r="A19" s="149" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="145"/>
-      <c r="C19" s="145"/>
-      <c r="D19" s="145"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="149"/>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -7034,7 +7032,7 @@
         <f>30941/2</f>
         <v>15470.5</v>
       </c>
-      <c r="F20" s="154" t="s">
+      <c r="F20" s="147" t="s">
         <v>112</v>
       </c>
     </row>
@@ -7053,7 +7051,7 @@
         <f>42620/2</f>
         <v>21310</v>
       </c>
-      <c r="F21" s="154"/>
+      <c r="F21" s="147"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="74">
@@ -7070,7 +7068,7 @@
         <f>62797/2</f>
         <v>31398.5</v>
       </c>
-      <c r="F22" s="154"/>
+      <c r="F22" s="147"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="75">
@@ -7087,7 +7085,7 @@
         <f>119146/2</f>
         <v>59573</v>
       </c>
-      <c r="F23" s="154"/>
+      <c r="F23" s="147"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="75">
@@ -7104,7 +7102,7 @@
         <f>141849/2</f>
         <v>70924.5</v>
       </c>
-      <c r="F24" s="154"/>
+      <c r="F24" s="147"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="75">
@@ -7121,7 +7119,7 @@
         <f>158086/2</f>
         <v>79043</v>
       </c>
-      <c r="F25" s="154"/>
+      <c r="F25" s="147"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
@@ -7135,38 +7133,38 @@
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="146" t="s">
+      <c r="A28" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="146" t="s">
+      <c r="C28" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="147" t="s">
+      <c r="D28" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="147" t="s">
+      <c r="E28" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="146"/>
-      <c r="B29" s="146"/>
-      <c r="C29" s="146"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147"/>
+      <c r="A29" s="150"/>
+      <c r="B29" s="150"/>
+      <c r="C29" s="150"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="144"/>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="145" t="s">
+      <c r="A30" s="149" t="s">
         <v>226</v>
       </c>
-      <c r="B30" s="145"/>
-      <c r="C30" s="145"/>
-      <c r="D30" s="145"/>
+      <c r="B30" s="149"/>
+      <c r="C30" s="149"/>
+      <c r="D30" s="149"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="159" t="s">
+      <c r="F30" s="156" t="s">
         <v>227</v>
       </c>
     </row>
@@ -7181,10 +7179,10 @@
         <v>257</v>
       </c>
       <c r="D31" s="25"/>
-      <c r="E31" s="119">
+      <c r="E31" s="118">
         <v>28194</v>
       </c>
-      <c r="F31" s="159"/>
+      <c r="F31" s="156"/>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="74">
@@ -7200,7 +7198,7 @@
       <c r="E32" s="98">
         <v>52715.399999999994</v>
       </c>
-      <c r="F32" s="159"/>
+      <c r="F32" s="156"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="76">
@@ -7216,7 +7214,7 @@
       <c r="E33" s="98">
         <v>178343.19999999995</v>
       </c>
-      <c r="F33" s="159"/>
+      <c r="F33" s="156"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="99">
@@ -7232,7 +7230,7 @@
       <c r="E34" s="98">
         <v>104645.19999999995</v>
       </c>
-      <c r="F34" s="159"/>
+      <c r="F34" s="156"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="101"/>
@@ -7247,42 +7245,42 @@
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="152"/>
-      <c r="C37" s="152"/>
-      <c r="D37" s="152"/>
+      <c r="B37" s="145"/>
+      <c r="C37" s="145"/>
+      <c r="D37" s="145"/>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="146" t="s">
+      <c r="A38" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="146" t="s">
+      <c r="C38" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D38" s="147" t="s">
+      <c r="D38" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E38" s="147" t="s">
+      <c r="E38" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="146"/>
-      <c r="B39" s="146"/>
-      <c r="C39" s="146"/>
-      <c r="D39" s="147"/>
-      <c r="E39" s="147"/>
+      <c r="A39" s="150"/>
+      <c r="B39" s="150"/>
+      <c r="C39" s="150"/>
+      <c r="D39" s="144"/>
+      <c r="E39" s="144"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="145" t="s">
+      <c r="A40" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="B40" s="145"/>
-      <c r="C40" s="145"/>
-      <c r="D40" s="145"/>
+      <c r="B40" s="149"/>
+      <c r="C40" s="149"/>
+      <c r="D40" s="149"/>
       <c r="E40" s="3"/>
       <c r="F40" s="21"/>
     </row>
@@ -7300,7 +7298,7 @@
       <c r="E41" s="89">
         <v>6198</v>
       </c>
-      <c r="F41" s="160" t="s">
+      <c r="F41" s="169" t="s">
         <v>27</v>
       </c>
     </row>
@@ -7318,7 +7316,7 @@
       <c r="E42" s="89">
         <v>6781.5</v>
       </c>
-      <c r="F42" s="160"/>
+      <c r="F42" s="169"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="87">
@@ -7334,7 +7332,7 @@
       <c r="E43" s="89">
         <v>8442.5</v>
       </c>
-      <c r="F43" s="160"/>
+      <c r="F43" s="169"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="87">
@@ -7350,7 +7348,7 @@
       <c r="E44" s="89">
         <v>12205</v>
       </c>
-      <c r="F44" s="160"/>
+      <c r="F44" s="169"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="87">
@@ -7366,7 +7364,7 @@
       <c r="E45" s="89">
         <v>12644</v>
       </c>
-      <c r="F45" s="160"/>
+      <c r="F45" s="169"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="87">
@@ -7379,10 +7377,10 @@
         <v>29</v>
       </c>
       <c r="D46" s="68"/>
-      <c r="E46" s="104">
-        <v>81760</v>
-      </c>
-      <c r="F46" s="160"/>
+      <c r="E46" s="119">
+        <v>33104</v>
+      </c>
+      <c r="F46" s="169"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="33"/>
@@ -7390,43 +7388,43 @@
       <c r="C47" s="57"/>
       <c r="D47" s="35"/>
       <c r="E47" s="67"/>
-      <c r="F47" s="160"/>
+      <c r="F47" s="169"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D48" s="6"/>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B49" s="146" t="s">
+      <c r="A49" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="146" t="s">
+      <c r="C49" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D49" s="147" t="s">
+      <c r="D49" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E49" s="147" t="s">
+      <c r="E49" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="146"/>
-      <c r="B50" s="146"/>
-      <c r="C50" s="146"/>
-      <c r="D50" s="147"/>
-      <c r="E50" s="147"/>
+      <c r="A50" s="150"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="150"/>
+      <c r="D50" s="144"/>
+      <c r="E50" s="144"/>
     </row>
     <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="145" t="s">
+      <c r="A51" s="149" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="145"/>
-      <c r="C51" s="145"/>
-      <c r="D51" s="145"/>
+      <c r="B51" s="149"/>
+      <c r="C51" s="149"/>
+      <c r="D51" s="149"/>
       <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -7458,7 +7456,7 @@
       <c r="E53" s="85">
         <v>8906.5</v>
       </c>
-      <c r="F53" s="160" t="s">
+      <c r="F53" s="169" t="s">
         <v>80</v>
       </c>
     </row>
@@ -7476,7 +7474,7 @@
       <c r="E54" s="84">
         <v>10470</v>
       </c>
-      <c r="F54" s="160"/>
+      <c r="F54" s="169"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="50">
@@ -7492,7 +7490,7 @@
       <c r="E55" s="85">
         <v>11218.5</v>
       </c>
-      <c r="F55" s="160"/>
+      <c r="F55" s="169"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="34">
@@ -7505,10 +7503,10 @@
         <v>41</v>
       </c>
       <c r="D56" s="46"/>
-      <c r="E56" s="105">
+      <c r="E56" s="104">
         <v>24616</v>
       </c>
-      <c r="F56" s="160"/>
+      <c r="F56" s="169"/>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
@@ -7516,7 +7514,7 @@
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
       <c r="E57" s="67"/>
-      <c r="F57" s="160"/>
+      <c r="F57" s="169"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D58" s="3"/>
@@ -7527,36 +7525,36 @@
       <c r="D59"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" s="146" t="s">
+      <c r="A60" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C60" s="146" t="s">
+      <c r="C60" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D60" s="147" t="s">
+      <c r="D60" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E60" s="147" t="s">
+      <c r="E60" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="146"/>
-      <c r="B61" s="146"/>
-      <c r="C61" s="146"/>
-      <c r="D61" s="147"/>
-      <c r="E61" s="147"/>
+      <c r="A61" s="150"/>
+      <c r="B61" s="150"/>
+      <c r="C61" s="150"/>
+      <c r="D61" s="144"/>
+      <c r="E61" s="144"/>
     </row>
     <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="145" t="s">
+      <c r="A62" s="149" t="s">
         <v>114</v>
       </c>
-      <c r="B62" s="145"/>
-      <c r="C62" s="145"/>
-      <c r="D62" s="145"/>
+      <c r="B62" s="149"/>
+      <c r="C62" s="149"/>
+      <c r="D62" s="149"/>
       <c r="E62" s="3"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -7573,7 +7571,7 @@
       <c r="E63" s="73">
         <v>8480</v>
       </c>
-      <c r="F63" s="153" t="s">
+      <c r="F63" s="146" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7591,7 +7589,7 @@
       <c r="E64" s="73">
         <v>13028</v>
       </c>
-      <c r="F64" s="153"/>
+      <c r="F64" s="146"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="46">
@@ -7607,7 +7605,7 @@
       <c r="E65" s="73">
         <v>14070.5</v>
       </c>
-      <c r="F65" s="153"/>
+      <c r="F65" s="146"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="46">
@@ -7628,45 +7626,45 @@
       <c r="A67" s="95"/>
       <c r="B67" s="96"/>
       <c r="C67" s="93"/>
-      <c r="D67" s="106"/>
+      <c r="D67" s="105"/>
       <c r="E67" s="94"/>
     </row>
     <row r="68" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B68" s="146" t="s">
+      <c r="A68" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B68" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C68" s="146" t="s">
+      <c r="C68" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D68" s="147" t="s">
+      <c r="D68" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="E68" s="147" t="s">
+      <c r="E68" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="146"/>
-      <c r="B69" s="146"/>
-      <c r="C69" s="146"/>
-      <c r="D69" s="147"/>
-      <c r="E69" s="147"/>
-      <c r="F69" s="153" t="s">
+      <c r="A69" s="150"/>
+      <c r="B69" s="150"/>
+      <c r="C69" s="150"/>
+      <c r="D69" s="144"/>
+      <c r="E69" s="144"/>
+      <c r="F69" s="146" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="145" t="s">
+      <c r="A70" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B70" s="145"/>
-      <c r="C70" s="145"/>
-      <c r="D70" s="145"/>
+      <c r="B70" s="149"/>
+      <c r="C70" s="149"/>
+      <c r="D70" s="149"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="153"/>
+      <c r="F70" s="146"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
@@ -7684,7 +7682,7 @@
       <c r="E71" s="14">
         <v>1232</v>
       </c>
-      <c r="F71" s="153"/>
+      <c r="F71" s="146"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="11">
@@ -7702,14 +7700,14 @@
       <c r="E72" s="14">
         <v>720</v>
       </c>
-      <c r="F72" s="153"/>
+      <c r="F72" s="146"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D73"/>
     </row>
     <row r="74" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A74" s="4"/>
-      <c r="C74" s="107" t="s">
+      <c r="C74" s="106" t="s">
         <v>54</v>
       </c>
       <c r="D74"/>
@@ -7746,7 +7744,7 @@
       <c r="D84"/>
     </row>
     <row r="85" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C85" s="107" t="s">
+      <c r="C85" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D85"/>
@@ -7840,26 +7838,22 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="B6:E9"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="F69:F72"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F63:F65"/>
+    <mergeCell ref="F53:F57"/>
+    <mergeCell ref="F41:F47"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="F20:F25"/>
     <mergeCell ref="F30:F34"/>
@@ -7876,22 +7870,26 @@
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="C38:C39"/>
     <mergeCell ref="D38:D39"/>
-    <mergeCell ref="F69:F72"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="F63:F65"/>
-    <mergeCell ref="F53:F57"/>
-    <mergeCell ref="F41:F47"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B6:E9"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7915,44 +7913,44 @@
   </cols>
   <sheetData>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="148" t="s">
+      <c r="B7" s="153" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="148"/>
+      <c r="C7" s="153"/>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="148"/>
-      <c r="C8" s="148"/>
+      <c r="B8" s="153"/>
+      <c r="C8" s="153"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="146" t="s">
+      <c r="A10" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="180" t="s">
+      <c r="D10" s="179" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="146"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="180"/>
+      <c r="A11" s="150"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="179"/>
       <c r="H11" s="6">
         <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="149" t="s">
+      <c r="A12" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="B12" s="149"/>
-      <c r="C12" s="149"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
       <c r="D12" s="26"/>
     </row>
     <row r="13" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7965,64 +7963,64 @@
       <c r="C13" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="144"/>
-      <c r="E13" s="159" t="s">
+      <c r="D13" s="143"/>
+      <c r="E13" s="156" t="s">
         <v>135</v>
       </c>
       <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="181" t="s">
+      <c r="A14" s="180" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="181"/>
+      <c r="B14" s="180"/>
       <c r="C14" s="17"/>
-      <c r="D14" s="144">
+      <c r="D14" s="143">
         <v>98000</v>
       </c>
-      <c r="E14" s="159"/>
+      <c r="E14" s="156"/>
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="159"/>
+      <c r="E15" s="156"/>
       <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="146" t="s">
+      <c r="A16" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="146" t="s">
+      <c r="C16" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="180" t="s">
+      <c r="D16" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="10"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="146"/>
-      <c r="B17" s="146"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="180"/>
+      <c r="A17" s="150"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="179"/>
       <c r="F17" s="10"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="145" t="s">
+      <c r="A18" s="149" t="s">
         <v>136</v>
       </c>
-      <c r="B18" s="145"/>
-      <c r="C18" s="145"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="149"/>
       <c r="D18" s="2"/>
       <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="116">
+      <c r="A19" s="115">
         <v>1</v>
       </c>
       <c r="B19" s="44" t="s">
@@ -8035,13 +8033,13 @@
         <f>33269/2</f>
         <v>16634.5</v>
       </c>
-      <c r="E19" s="154" t="s">
+      <c r="E19" s="147" t="s">
         <v>137</v>
       </c>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="116">
+      <c r="A20" s="115">
         <v>1</v>
       </c>
       <c r="B20" s="44" t="s">
@@ -8054,11 +8052,11 @@
         <f>46560/2</f>
         <v>23280</v>
       </c>
-      <c r="E20" s="154"/>
+      <c r="E20" s="147"/>
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="116">
+      <c r="A21" s="115">
         <v>1</v>
       </c>
       <c r="B21" s="44" t="s">
@@ -8071,11 +8069,11 @@
         <f>52529/2</f>
         <v>26264.5</v>
       </c>
-      <c r="E21" s="154"/>
+      <c r="E21" s="147"/>
       <c r="F21" s="10"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="116">
+      <c r="A22" s="115">
         <v>1</v>
       </c>
       <c r="B22" s="44" t="s">
@@ -8088,11 +8086,11 @@
         <f>70756/2</f>
         <v>35378</v>
       </c>
-      <c r="E22" s="154"/>
+      <c r="E22" s="147"/>
       <c r="F22" s="10"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="116">
+      <c r="A23" s="115">
         <v>1</v>
       </c>
       <c r="B23" s="44" t="s">
@@ -8105,11 +8103,11 @@
         <f>80386/2</f>
         <v>40193</v>
       </c>
-      <c r="E23" s="154"/>
+      <c r="E23" s="147"/>
       <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="116">
+      <c r="A24" s="115">
         <v>1</v>
       </c>
       <c r="B24" s="44" t="s">
@@ -8118,11 +8116,11 @@
       <c r="C24" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="108">
+      <c r="D24" s="107">
         <f>115525/2</f>
         <v>57762.5</v>
       </c>
-      <c r="E24" s="154"/>
+      <c r="E24" s="147"/>
       <c r="F24" s="10"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -8130,41 +8128,41 @@
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="67"/>
-      <c r="E25" s="154"/>
+      <c r="E25" s="147"/>
       <c r="F25" s="10"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="146" t="s">
+      <c r="A28" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="146" t="s">
+      <c r="C28" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D28" s="180" t="s">
+      <c r="D28" s="179" t="s">
         <v>5</v>
       </c>
       <c r="E28" s="22"/>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="146"/>
-      <c r="B29" s="146"/>
-      <c r="C29" s="146"/>
-      <c r="D29" s="180"/>
-      <c r="E29" s="153" t="s">
+      <c r="A29" s="150"/>
+      <c r="B29" s="150"/>
+      <c r="C29" s="150"/>
+      <c r="D29" s="179"/>
+      <c r="E29" s="146" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="145" t="s">
+      <c r="A30" s="149" t="s">
         <v>234</v>
       </c>
-      <c r="B30" s="145"/>
-      <c r="C30" s="145"/>
+      <c r="B30" s="149"/>
+      <c r="C30" s="149"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="153"/>
+      <c r="E30" s="146"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
@@ -8176,10 +8174,10 @@
       <c r="C31" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D31" s="119">
+      <c r="D31" s="118">
         <v>28194</v>
       </c>
-      <c r="E31" s="153"/>
+      <c r="E31" s="146"/>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
@@ -8194,7 +8192,7 @@
       <c r="D32" s="81">
         <v>52715.399999999994</v>
       </c>
-      <c r="E32" s="153"/>
+      <c r="E32" s="146"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
@@ -8209,7 +8207,7 @@
       <c r="D33" s="81">
         <v>178343.19999999995</v>
       </c>
-      <c r="E33" s="153"/>
+      <c r="E33" s="146"/>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
@@ -8221,50 +8219,50 @@
       <c r="C34" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="109">
+      <c r="D34" s="108">
         <v>104645.19999999995</v>
       </c>
-      <c r="E34" s="153"/>
+      <c r="E34" s="146"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="153"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="146"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D37" s="2"/>
       <c r="F37" s="10"/>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="146" t="s">
+      <c r="A38" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="146" t="s">
+      <c r="C38" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D38" s="180" t="s">
+      <c r="D38" s="179" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="10"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="146"/>
-      <c r="B39" s="146"/>
-      <c r="C39" s="146"/>
-      <c r="D39" s="180"/>
+      <c r="A39" s="150"/>
+      <c r="B39" s="150"/>
+      <c r="C39" s="150"/>
+      <c r="D39" s="179"/>
       <c r="F39" s="10"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="145" t="s">
+      <c r="A40" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="B40" s="145"/>
-      <c r="C40" s="145"/>
+      <c r="B40" s="149"/>
+      <c r="C40" s="149"/>
       <c r="D40" s="2"/>
       <c r="F40" s="10"/>
     </row>
@@ -8281,7 +8279,7 @@
       <c r="D41" s="89">
         <v>6198</v>
       </c>
-      <c r="E41" s="160" t="s">
+      <c r="E41" s="169" t="s">
         <v>27</v>
       </c>
       <c r="F41" s="10"/>
@@ -8299,7 +8297,7 @@
       <c r="D42" s="89">
         <v>6781.5</v>
       </c>
-      <c r="E42" s="160"/>
+      <c r="E42" s="169"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="87">
@@ -8314,7 +8312,7 @@
       <c r="D43" s="89">
         <v>8442.5</v>
       </c>
-      <c r="E43" s="160"/>
+      <c r="E43" s="169"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="87">
@@ -8329,7 +8327,7 @@
       <c r="D44" s="89">
         <v>12205</v>
       </c>
-      <c r="E44" s="160"/>
+      <c r="E44" s="169"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="87">
@@ -8344,7 +8342,7 @@
       <c r="D45" s="89">
         <v>12644</v>
       </c>
-      <c r="E45" s="160"/>
+      <c r="E45" s="169"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="87">
@@ -8356,50 +8354,50 @@
       <c r="C46" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D46" s="104">
-        <v>81760</v>
-      </c>
-      <c r="E46" s="160"/>
+      <c r="D46" s="119">
+        <v>33104</v>
+      </c>
+      <c r="E46" s="169"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="67"/>
-      <c r="E47" s="160"/>
+      <c r="E47" s="169"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E48" s="160"/>
+      <c r="E48" s="169"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B50" s="146" t="s">
+      <c r="A50" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="146" t="s">
+      <c r="C50" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D50" s="180" t="s">
+      <c r="D50" s="179" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="146"/>
-      <c r="B51" s="146"/>
-      <c r="C51" s="146"/>
-      <c r="D51" s="180"/>
+      <c r="A51" s="150"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="150"/>
+      <c r="D51" s="179"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="145" t="s">
+      <c r="A52" s="149" t="s">
         <v>230</v>
       </c>
-      <c r="B52" s="145"/>
-      <c r="C52" s="145"/>
+      <c r="B52" s="149"/>
+      <c r="C52" s="149"/>
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -8429,7 +8427,7 @@
       <c r="D54" s="85">
         <v>8906.5</v>
       </c>
-      <c r="E54" s="160" t="s">
+      <c r="E54" s="169" t="s">
         <v>231</v>
       </c>
     </row>
@@ -8446,7 +8444,7 @@
       <c r="D55" s="84">
         <v>10470</v>
       </c>
-      <c r="E55" s="160"/>
+      <c r="E55" s="169"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="50">
@@ -8461,7 +8459,7 @@
       <c r="D56" s="85">
         <v>11218.5</v>
       </c>
-      <c r="E56" s="160"/>
+      <c r="E56" s="169"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="34">
@@ -8473,47 +8471,47 @@
       <c r="C57" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D57" s="105">
+      <c r="D57" s="104">
         <v>24616</v>
       </c>
-      <c r="E57" s="160"/>
+      <c r="E57" s="169"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
       <c r="D58" s="67"/>
-      <c r="E58" s="160"/>
+      <c r="E58" s="169"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61" s="146" t="s">
+      <c r="A61" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B61" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="146" t="s">
+      <c r="C61" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D61" s="180" t="s">
+      <c r="D61" s="179" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="146"/>
-      <c r="B62" s="146"/>
-      <c r="C62" s="146"/>
-      <c r="D62" s="180"/>
+      <c r="A62" s="150"/>
+      <c r="B62" s="150"/>
+      <c r="C62" s="150"/>
+      <c r="D62" s="179"/>
     </row>
     <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="145" t="s">
+      <c r="A63" s="149" t="s">
         <v>232</v>
       </c>
-      <c r="B63" s="145"/>
-      <c r="C63" s="145"/>
+      <c r="B63" s="149"/>
+      <c r="C63" s="149"/>
       <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -8543,7 +8541,7 @@
       <c r="D65" s="14">
         <v>13028</v>
       </c>
-      <c r="E65" s="153" t="s">
+      <c r="E65" s="146" t="s">
         <v>42</v>
       </c>
     </row>
@@ -8560,7 +8558,7 @@
       <c r="D66" s="14">
         <v>14070.5</v>
       </c>
-      <c r="E66" s="153"/>
+      <c r="E66" s="146"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="11">
@@ -8575,7 +8573,7 @@
       <c r="D67" s="14">
         <v>23773</v>
       </c>
-      <c r="E67" s="153"/>
+      <c r="E67" s="146"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
@@ -8584,36 +8582,36 @@
       <c r="D68" s="11"/>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B70" s="146" t="s">
+      <c r="A70" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B70" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C70" s="146" t="s">
+      <c r="C70" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D70" s="180" t="s">
+      <c r="D70" s="179" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="146"/>
-      <c r="B71" s="146"/>
-      <c r="C71" s="146"/>
-      <c r="D71" s="180"/>
-      <c r="E71" s="154" t="s">
+      <c r="A71" s="150"/>
+      <c r="B71" s="150"/>
+      <c r="C71" s="150"/>
+      <c r="D71" s="179"/>
+      <c r="E71" s="147" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="145" t="s">
+      <c r="A72" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B72" s="145"/>
-      <c r="C72" s="145"/>
+      <c r="B72" s="149"/>
+      <c r="C72" s="149"/>
       <c r="D72" s="25"/>
-      <c r="E72" s="154"/>
+      <c r="E72" s="147"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
@@ -8628,7 +8626,7 @@
       <c r="D73" s="14">
         <v>1232</v>
       </c>
-      <c r="E73" s="154"/>
+      <c r="E73" s="147"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
@@ -8649,12 +8647,12 @@
       <c r="F75" s="28"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C76" s="107" t="s">
+      <c r="C76" s="106" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="86" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C86" s="107" t="s">
+      <c r="C86" s="106" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8675,36 +8673,11 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="E65:E67"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="E41:E48"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="D28:D29"/>
     <mergeCell ref="E13:E15"/>
     <mergeCell ref="A14:B14"/>
@@ -8714,11 +8687,36 @@
     <mergeCell ref="D16:D17"/>
     <mergeCell ref="E19:E25"/>
     <mergeCell ref="E29:E35"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="E41:E48"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="E54:E58"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="E65:E67"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="A72:C72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8741,48 +8739,48 @@
   </cols>
   <sheetData>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="148" t="s">
+      <c r="B7" s="153" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="148"/>
+      <c r="C7" s="153"/>
       <c r="D7" s="24"/>
     </row>
     <row r="8" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="148"/>
-      <c r="C8" s="148"/>
+      <c r="B8" s="153"/>
+      <c r="C8" s="153"/>
       <c r="D8" s="24"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="146" t="s">
+      <c r="A10" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="147" t="s">
+      <c r="D10" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="146"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="147"/>
+      <c r="A11" s="150"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="144"/>
       <c r="G11" s="8">
         <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="149" t="s">
+      <c r="A12" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="B12" s="149"/>
-      <c r="C12" s="149"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="154"/>
       <c r="D12" s="26"/>
-      <c r="E12" s="159" t="s">
+      <c r="E12" s="156" t="s">
         <v>255</v>
       </c>
     </row>
@@ -8797,48 +8795,48 @@
         <v>149</v>
       </c>
       <c r="D13" s="17"/>
-      <c r="E13" s="159"/>
+      <c r="E13" s="156"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="167" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="162"/>
+      <c r="B14" s="168"/>
       <c r="C14" s="20"/>
       <c r="D14" s="14">
         <v>82000</v>
       </c>
-      <c r="E14" s="159"/>
+      <c r="E14" s="156"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D15"/>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="146" t="s">
+      <c r="A16" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="146" t="s">
+      <c r="C16" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="147" t="s">
+      <c r="D16" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="146"/>
-      <c r="B17" s="146"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="147"/>
+      <c r="A17" s="150"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="144"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="145" t="s">
+      <c r="A18" s="149" t="s">
         <v>235</v>
       </c>
-      <c r="B18" s="145"/>
-      <c r="C18" s="145"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="149"/>
       <c r="D18" s="25"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -8855,7 +8853,7 @@
         <f>30941/2</f>
         <v>15470.5</v>
       </c>
-      <c r="E19" s="160" t="s">
+      <c r="E19" s="169" t="s">
         <v>137</v>
       </c>
     </row>
@@ -8873,7 +8871,7 @@
         <f>42620/2</f>
         <v>21310</v>
       </c>
-      <c r="E20" s="160"/>
+      <c r="E20" s="169"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="48">
@@ -8889,7 +8887,7 @@
         <f>48590/2</f>
         <v>24295</v>
       </c>
-      <c r="E21" s="160"/>
+      <c r="E21" s="169"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="48">
@@ -8905,7 +8903,7 @@
         <f>62797/2</f>
         <v>31398.5</v>
       </c>
-      <c r="E22" s="160"/>
+      <c r="E22" s="169"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="48">
@@ -8921,7 +8919,7 @@
         <f>75511/2</f>
         <v>37755.5</v>
       </c>
-      <c r="E23" s="160"/>
+      <c r="E23" s="169"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="48">
@@ -8937,7 +8935,7 @@
         <f>100661/2</f>
         <v>50330.5</v>
       </c>
-      <c r="E24" s="160"/>
+      <c r="E24" s="169"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="48">
@@ -8953,7 +8951,7 @@
         <f>119146/2</f>
         <v>59573</v>
       </c>
-      <c r="E25" s="160"/>
+      <c r="E25" s="169"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
@@ -8965,54 +8963,54 @@
       <c r="C26" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="111">
+      <c r="D26" s="110">
         <f>135880/2</f>
         <v>67940</v>
       </c>
-      <c r="E26" s="160"/>
+      <c r="E26" s="169"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="67"/>
-      <c r="E27" s="160"/>
+      <c r="E27" s="169"/>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="6"/>
       <c r="E28" s="22"/>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="146" t="s">
+      <c r="A29" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="146" t="s">
+      <c r="C29" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="147" t="s">
+      <c r="D29" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="146"/>
-      <c r="B30" s="146"/>
-      <c r="C30" s="146"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="153" t="s">
+      <c r="A30" s="150"/>
+      <c r="B30" s="150"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="144"/>
+      <c r="E30" s="146" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="145" t="s">
+      <c r="A31" s="149" t="s">
         <v>236</v>
       </c>
-      <c r="B31" s="145"/>
-      <c r="C31" s="145"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149"/>
       <c r="D31" s="25"/>
-      <c r="E31" s="153"/>
+      <c r="E31" s="146"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
@@ -9024,10 +9022,10 @@
       <c r="C32" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D32" s="119">
+      <c r="D32" s="118">
         <v>28194</v>
       </c>
-      <c r="E32" s="153"/>
+      <c r="E32" s="146"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
@@ -9042,7 +9040,7 @@
       <c r="D33" s="81">
         <v>52715.399999999994</v>
       </c>
-      <c r="E33" s="153"/>
+      <c r="E33" s="146"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
@@ -9057,7 +9055,7 @@
       <c r="D34" s="81">
         <v>178343.19999999995</v>
       </c>
-      <c r="E34" s="153"/>
+      <c r="E34" s="146"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
@@ -9069,17 +9067,17 @@
       <c r="C35" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D35" s="109">
+      <c r="D35" s="108">
         <v>104645.19999999995</v>
       </c>
-      <c r="E35" s="153"/>
+      <c r="E35" s="146"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
       <c r="D36" s="67"/>
-      <c r="E36" s="153"/>
+      <c r="E36" s="146"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D37" s="3"/>
@@ -9088,33 +9086,33 @@
       <c r="D38" s="3"/>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="146" t="s">
+      <c r="A39" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B39" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="146" t="s">
+      <c r="C39" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="147" t="s">
+      <c r="D39" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="146"/>
-      <c r="B40" s="146"/>
-      <c r="C40" s="146"/>
-      <c r="D40" s="147"/>
+      <c r="A40" s="150"/>
+      <c r="B40" s="150"/>
+      <c r="C40" s="150"/>
+      <c r="D40" s="144"/>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="145" t="s">
+      <c r="A41" s="149" t="s">
         <v>237</v>
       </c>
-      <c r="B41" s="145"/>
-      <c r="C41" s="145"/>
+      <c r="B41" s="149"/>
+      <c r="C41" s="149"/>
       <c r="D41" s="25"/>
-      <c r="E41" s="160" t="s">
+      <c r="E41" s="169" t="s">
         <v>27</v>
       </c>
     </row>
@@ -9131,7 +9129,7 @@
       <c r="D42" s="14">
         <v>6198</v>
       </c>
-      <c r="E42" s="160"/>
+      <c r="E42" s="169"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
@@ -9146,7 +9144,7 @@
       <c r="D43" s="14">
         <v>6781.5</v>
       </c>
-      <c r="E43" s="160"/>
+      <c r="E43" s="169"/>
       <c r="F43" s="53"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -9162,7 +9160,7 @@
       <c r="D44" s="14">
         <v>8442.5</v>
       </c>
-      <c r="E44" s="160"/>
+      <c r="E44" s="169"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
@@ -9174,10 +9172,10 @@
       <c r="C45" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D45" s="14">
-        <v>12205</v>
-      </c>
-      <c r="E45" s="160"/>
+      <c r="D45" s="119">
+        <v>33104</v>
+      </c>
+      <c r="E45" s="169"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
@@ -9190,16 +9188,16 @@
         <v>31</v>
       </c>
       <c r="D46" s="14">
-        <v>12644</v>
-      </c>
-      <c r="E46" s="160"/>
+        <v>44000</v>
+      </c>
+      <c r="E46" s="169"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="11"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="67"/>
-      <c r="E47" s="160"/>
+      <c r="E47" s="169"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D48"/>
@@ -9208,33 +9206,33 @@
       <c r="D49" s="6"/>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B50" s="146" t="s">
+      <c r="A50" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="146" t="s">
+      <c r="C50" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D50" s="147" t="s">
+      <c r="D50" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="146"/>
-      <c r="B51" s="146"/>
-      <c r="C51" s="146"/>
-      <c r="D51" s="147"/>
+      <c r="A51" s="150"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="150"/>
+      <c r="D51" s="144"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="145" t="s">
+      <c r="A52" s="149" t="s">
         <v>157</v>
       </c>
-      <c r="B52" s="145"/>
-      <c r="C52" s="145"/>
+      <c r="B52" s="149"/>
+      <c r="C52" s="149"/>
       <c r="D52" s="25"/>
-      <c r="E52" s="160" t="s">
+      <c r="E52" s="169" t="s">
         <v>80</v>
       </c>
     </row>
@@ -9251,7 +9249,7 @@
       <c r="D53" s="14">
         <v>4595.5</v>
       </c>
-      <c r="E53" s="160"/>
+      <c r="E53" s="169"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
@@ -9266,7 +9264,7 @@
       <c r="D54" s="14">
         <v>8906.5</v>
       </c>
-      <c r="E54" s="160"/>
+      <c r="E54" s="169"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
@@ -9281,7 +9279,7 @@
       <c r="D55" s="14">
         <v>10470</v>
       </c>
-      <c r="E55" s="160"/>
+      <c r="E55" s="169"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
@@ -9296,7 +9294,7 @@
       <c r="D56" s="14">
         <v>11218.5</v>
       </c>
-      <c r="E56" s="160"/>
+      <c r="E56" s="169"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
@@ -9311,7 +9309,7 @@
       <c r="D57" s="14">
         <v>24616</v>
       </c>
-      <c r="E57" s="160"/>
+      <c r="E57" s="169"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D58" s="3"/>
@@ -9320,33 +9318,33 @@
       <c r="D59"/>
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" s="146" t="s">
+      <c r="A60" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B60" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C60" s="146" t="s">
+      <c r="C60" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D60" s="147" t="s">
+      <c r="D60" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="146"/>
-      <c r="B61" s="146"/>
-      <c r="C61" s="146"/>
-      <c r="D61" s="147"/>
+      <c r="A61" s="150"/>
+      <c r="B61" s="150"/>
+      <c r="C61" s="150"/>
+      <c r="D61" s="144"/>
     </row>
     <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="145" t="s">
+      <c r="A62" s="149" t="s">
         <v>238</v>
       </c>
-      <c r="B62" s="145"/>
-      <c r="C62" s="145"/>
+      <c r="B62" s="149"/>
+      <c r="C62" s="149"/>
       <c r="D62" s="25"/>
-      <c r="E62" s="154" t="s">
+      <c r="E62" s="147" t="s">
         <v>42</v>
       </c>
     </row>
@@ -9363,7 +9361,7 @@
       <c r="D63" s="14">
         <v>8480</v>
       </c>
-      <c r="E63" s="154"/>
+      <c r="E63" s="147"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
@@ -9378,7 +9376,7 @@
       <c r="D64" s="14">
         <v>13028</v>
       </c>
-      <c r="E64" s="154"/>
+      <c r="E64" s="147"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
@@ -9393,7 +9391,7 @@
       <c r="D65" s="14">
         <v>14070.5</v>
       </c>
-      <c r="E65" s="154"/>
+      <c r="E65" s="147"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
@@ -9408,49 +9406,49 @@
       <c r="D66" s="14">
         <v>23773</v>
       </c>
-      <c r="E66" s="154"/>
+      <c r="E66" s="147"/>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="3"/>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" s="146" t="s">
+      <c r="A69" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="146" t="s">
+      <c r="C69" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="147" t="s">
+      <c r="D69" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="146"/>
-      <c r="B70" s="146"/>
-      <c r="C70" s="146"/>
-      <c r="D70" s="147"/>
-      <c r="E70" s="154" t="s">
+      <c r="A70" s="150"/>
+      <c r="B70" s="150"/>
+      <c r="C70" s="150"/>
+      <c r="D70" s="144"/>
+      <c r="E70" s="147" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="145" t="s">
+      <c r="A71" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B71" s="145"/>
-      <c r="C71" s="145"/>
+      <c r="B71" s="149"/>
+      <c r="C71" s="149"/>
       <c r="D71" s="25"/>
-      <c r="E71" s="154"/>
+      <c r="E71" s="147"/>
     </row>
     <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="25"/>
       <c r="B72" s="25"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
-      <c r="E72" s="154"/>
+      <c r="E72" s="147"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
@@ -9465,7 +9463,7 @@
       <c r="D73" s="14">
         <v>1232</v>
       </c>
-      <c r="E73" s="154"/>
+      <c r="E73" s="147"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
@@ -9480,21 +9478,21 @@
       <c r="D74" s="14">
         <v>720</v>
       </c>
-      <c r="E74" s="154"/>
+      <c r="E74" s="147"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="11"/>
       <c r="B75" s="11"/>
       <c r="C75" s="11"/>
       <c r="D75" s="67"/>
-      <c r="E75" s="154"/>
+      <c r="E75" s="147"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D76"/>
     </row>
     <row r="77" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
-      <c r="C77" s="107" t="s">
+      <c r="C77" s="106" t="s">
         <v>54</v>
       </c>
       <c r="D77"/>
@@ -9531,7 +9529,7 @@
       <c r="D87"/>
     </row>
     <row r="88" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C88" s="107" t="s">
+      <c r="C88" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D88"/>
@@ -9571,6 +9569,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="E19:E27"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E30:E36"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="E41:E47"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="E70:E75"/>
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="D50:D51"/>
@@ -9587,34 +9613,6 @@
     <mergeCell ref="C60:C61"/>
     <mergeCell ref="D60:D61"/>
     <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="E19:E27"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E30:E36"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="E41:E47"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9636,49 +9634,49 @@
   </cols>
   <sheetData>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="148"/>
-      <c r="C9" s="148"/>
+      <c r="B9" s="153"/>
+      <c r="C9" s="153"/>
       <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="148"/>
-      <c r="C10" s="148"/>
+      <c r="B10" s="153"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="24"/>
     </row>
     <row r="11" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="148"/>
-      <c r="C11" s="148"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="153"/>
       <c r="D11" s="24"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="146" t="s">
+      <c r="A13" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="147" t="s">
+      <c r="D13" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="146"/>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="147"/>
+      <c r="A14" s="150"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="144"/>
       <c r="G14" s="8">
         <v>0.4</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="149" t="s">
+      <c r="A15" s="154" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="149"/>
-      <c r="C15" s="149"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
       <c r="D15" s="26"/>
     </row>
     <row r="16" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9689,8 +9687,8 @@
       <c r="C16" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="142"/>
-      <c r="E16" s="159" t="s">
+      <c r="D16" s="141"/>
+      <c r="E16" s="156" t="s">
         <v>135</v>
       </c>
     </row>
@@ -9700,40 +9698,40 @@
       <c r="C17" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="143">
+      <c r="D17" s="142">
         <v>110000</v>
       </c>
-      <c r="E17" s="159"/>
+      <c r="E17" s="156"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="146" t="s">
+      <c r="A19" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="146" t="s">
+      <c r="C19" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D19" s="147" t="s">
+      <c r="D19" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="146"/>
-      <c r="B20" s="146"/>
-      <c r="C20" s="146"/>
-      <c r="D20" s="147"/>
+      <c r="A20" s="150"/>
+      <c r="B20" s="150"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="144"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="145" t="s">
+      <c r="A21" s="149" t="s">
         <v>158</v>
       </c>
-      <c r="B21" s="145"/>
-      <c r="C21" s="145"/>
+      <c r="B21" s="149"/>
+      <c r="C21" s="149"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9750,7 +9748,7 @@
         <f>33269/2</f>
         <v>16634.5</v>
       </c>
-      <c r="E22" s="160" t="s">
+      <c r="E22" s="169" t="s">
         <v>137</v>
       </c>
     </row>
@@ -9768,7 +9766,7 @@
         <f>46560/2</f>
         <v>23280</v>
       </c>
-      <c r="E23" s="160"/>
+      <c r="E23" s="169"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
@@ -9784,7 +9782,7 @@
         <f>52529/2</f>
         <v>26264.5</v>
       </c>
-      <c r="E24" s="160"/>
+      <c r="E24" s="169"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
@@ -9800,7 +9798,7 @@
         <f>70756/2</f>
         <v>35378</v>
       </c>
-      <c r="E25" s="160"/>
+      <c r="E25" s="169"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
@@ -9816,7 +9814,7 @@
         <f>80386/2</f>
         <v>40193</v>
       </c>
-      <c r="E26" s="160"/>
+      <c r="E26" s="169"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="43" t="s">
@@ -9828,18 +9826,18 @@
       <c r="C27" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="108">
+      <c r="D27" s="107">
         <f>115525/2</f>
         <v>57762.5</v>
       </c>
-      <c r="E27" s="160"/>
+      <c r="E27" s="169"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="67"/>
-      <c r="E28" s="160"/>
+      <c r="E28" s="169"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D29" s="3"/>
@@ -9849,34 +9847,34 @@
       <c r="E30" s="22"/>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="146" t="s">
+      <c r="A31" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="146" t="s">
+      <c r="C31" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="147" t="s">
+      <c r="D31" s="144" t="s">
         <v>5</v>
       </c>
       <c r="E31" s="22"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="146"/>
-      <c r="B32" s="146"/>
-      <c r="C32" s="146"/>
-      <c r="D32" s="147"/>
+      <c r="A32" s="150"/>
+      <c r="B32" s="150"/>
+      <c r="C32" s="150"/>
+      <c r="D32" s="144"/>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="145" t="s">
+      <c r="A33" s="149" t="s">
         <v>239</v>
       </c>
-      <c r="B33" s="145"/>
-      <c r="C33" s="145"/>
+      <c r="B33" s="149"/>
+      <c r="C33" s="149"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="153" t="s">
+      <c r="E33" s="146" t="s">
         <v>138</v>
       </c>
     </row>
@@ -9890,10 +9888,10 @@
       <c r="C34" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D34" s="119">
+      <c r="D34" s="118">
         <v>28194</v>
       </c>
-      <c r="E34" s="153"/>
+      <c r="E34" s="146"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
@@ -9908,7 +9906,7 @@
       <c r="D35" s="81">
         <v>52715.399999999994</v>
       </c>
-      <c r="E35" s="153"/>
+      <c r="E35" s="146"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
@@ -9923,7 +9921,7 @@
       <c r="D36" s="81">
         <v>178343.19999999995</v>
       </c>
-      <c r="E36" s="153"/>
+      <c r="E36" s="146"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
@@ -9935,47 +9933,47 @@
       <c r="C37" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="109">
+      <c r="D37" s="108">
         <v>104645.19999999995</v>
       </c>
-      <c r="E37" s="153"/>
+      <c r="E37" s="146"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
-      <c r="D38" s="112"/>
+      <c r="D38" s="111"/>
       <c r="E38" s="27"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D39"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B41" s="146" t="s">
+      <c r="A41" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D41" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="146"/>
-      <c r="B42" s="146"/>
-      <c r="C42" s="146"/>
-      <c r="D42" s="147"/>
+      <c r="A42" s="150"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="144"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="145" t="s">
+      <c r="A43" s="149" t="s">
         <v>240</v>
       </c>
-      <c r="B43" s="145"/>
-      <c r="C43" s="145"/>
+      <c r="B43" s="149"/>
+      <c r="C43" s="149"/>
       <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -9991,7 +9989,7 @@
       <c r="D44" s="89">
         <v>6198</v>
       </c>
-      <c r="E44" s="160" t="s">
+      <c r="E44" s="169" t="s">
         <v>27</v>
       </c>
     </row>
@@ -10008,7 +10006,7 @@
       <c r="D45" s="89">
         <v>6781.5</v>
       </c>
-      <c r="E45" s="160"/>
+      <c r="E45" s="169"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="87">
@@ -10023,7 +10021,7 @@
       <c r="D46" s="89">
         <v>8442.5</v>
       </c>
-      <c r="E46" s="160"/>
+      <c r="E46" s="169"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="87">
@@ -10038,7 +10036,7 @@
       <c r="D47" s="89">
         <v>12205</v>
       </c>
-      <c r="E47" s="160"/>
+      <c r="E47" s="169"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="87">
@@ -10053,7 +10051,7 @@
       <c r="D48" s="89">
         <v>12644</v>
       </c>
-      <c r="E48" s="160"/>
+      <c r="E48" s="169"/>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="87">
@@ -10065,44 +10063,44 @@
       <c r="C49" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="104">
-        <v>81760</v>
-      </c>
-      <c r="E49" s="160"/>
+      <c r="D49" s="119">
+        <v>33104</v>
+      </c>
+      <c r="E49" s="169"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="67"/>
-      <c r="E50" s="160"/>
+      <c r="E50" s="169"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B52" s="146" t="s">
+      <c r="A52" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="146" t="s">
+      <c r="C52" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D52" s="147" t="s">
+      <c r="D52" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="146"/>
-      <c r="B53" s="146"/>
-      <c r="C53" s="146"/>
-      <c r="D53" s="147"/>
+      <c r="A53" s="150"/>
+      <c r="B53" s="150"/>
+      <c r="C53" s="150"/>
+      <c r="D53" s="144"/>
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="145" t="s">
+      <c r="A54" s="149" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="145"/>
-      <c r="C54" s="145"/>
+      <c r="B54" s="149"/>
+      <c r="C54" s="149"/>
       <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -10157,7 +10155,7 @@
       <c r="C58" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="D58" s="105">
+      <c r="D58" s="104">
         <v>11218.5</v>
       </c>
     </row>
@@ -10168,10 +10166,10 @@
       <c r="B59" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C59" s="113" t="s">
+      <c r="C59" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D59" s="114">
+      <c r="D59" s="113">
         <v>24616</v>
       </c>
     </row>
@@ -10185,31 +10183,31 @@
       <c r="D61"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B63" s="146" t="s">
+      <c r="A63" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C63" s="146" t="s">
+      <c r="C63" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D63" s="147" t="s">
+      <c r="D63" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="146"/>
-      <c r="B64" s="146"/>
-      <c r="C64" s="146"/>
-      <c r="D64" s="147"/>
+      <c r="A64" s="150"/>
+      <c r="B64" s="150"/>
+      <c r="C64" s="150"/>
+      <c r="D64" s="144"/>
     </row>
     <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="145" t="s">
+      <c r="A65" s="149" t="s">
         <v>160</v>
       </c>
-      <c r="B65" s="145"/>
-      <c r="C65" s="145"/>
+      <c r="B65" s="149"/>
+      <c r="C65" s="149"/>
       <c r="D65" s="3"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -10239,7 +10237,7 @@
       <c r="D67" s="14">
         <v>13028</v>
       </c>
-      <c r="E67" s="153" t="s">
+      <c r="E67" s="146" t="s">
         <v>42</v>
       </c>
     </row>
@@ -10256,7 +10254,7 @@
       <c r="D68" s="14">
         <v>14070.5</v>
       </c>
-      <c r="E68" s="153"/>
+      <c r="E68" s="146"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
@@ -10271,7 +10269,7 @@
       <c r="D69" s="14">
         <v>23773</v>
       </c>
-      <c r="E69" s="153"/>
+      <c r="E69" s="146"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="11"/>
@@ -10283,38 +10281,38 @@
       <c r="D71"/>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B72" s="146" t="s">
+      <c r="A72" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="146" t="s">
+      <c r="C72" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D72" s="147" t="s">
+      <c r="D72" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="146"/>
-      <c r="B73" s="146"/>
-      <c r="C73" s="146"/>
-      <c r="D73" s="147"/>
-      <c r="E73" s="154" t="s">
+      <c r="A73" s="150"/>
+      <c r="B73" s="150"/>
+      <c r="C73" s="150"/>
+      <c r="D73" s="144"/>
+      <c r="E73" s="147" t="s">
         <v>51</v>
       </c>
-      <c r="F73" s="153"/>
+      <c r="F73" s="146"/>
     </row>
     <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="145" t="s">
+      <c r="A74" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B74" s="145"/>
-      <c r="C74" s="145"/>
+      <c r="B74" s="149"/>
+      <c r="C74" s="149"/>
       <c r="D74" s="25"/>
-      <c r="E74" s="154"/>
-      <c r="F74" s="153"/>
+      <c r="E74" s="147"/>
+      <c r="F74" s="146"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
@@ -10329,8 +10327,8 @@
       <c r="D75" s="14">
         <v>1232</v>
       </c>
-      <c r="E75" s="154"/>
-      <c r="F75" s="153"/>
+      <c r="E75" s="147"/>
+      <c r="F75" s="146"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
@@ -10345,23 +10343,23 @@
       <c r="D76" s="14">
         <v>720</v>
       </c>
-      <c r="E76" s="154"/>
-      <c r="F76" s="153"/>
+      <c r="E76" s="147"/>
+      <c r="F76" s="146"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="11"/>
       <c r="B77" s="11"/>
       <c r="C77" s="11"/>
       <c r="D77" s="67"/>
-      <c r="E77" s="154"/>
-      <c r="F77" s="153"/>
+      <c r="E77" s="147"/>
+      <c r="F77" s="146"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D78"/>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
-      <c r="C79" s="107" t="s">
+      <c r="C79" s="106" t="s">
         <v>54</v>
       </c>
       <c r="D79"/>
@@ -10398,7 +10396,7 @@
       <c r="D89"/>
     </row>
     <row r="90" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C90" s="107" t="s">
+      <c r="C90" s="106" t="s">
         <v>59</v>
       </c>
       <c r="D90"/>
@@ -10450,11 +10448,32 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="F73:F77"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="E67:E69"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E73:E77"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="E44:E50"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="E33:E37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="E22:E28"/>
@@ -10467,32 +10486,11 @@
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="D19:D20"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="E33:E37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="E44:E50"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="F73:F77"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="E67:E69"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E73:E77"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10515,33 +10513,33 @@
   </cols>
   <sheetData>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="148" t="s">
+      <c r="B9" s="153" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="148"/>
+      <c r="C9" s="153"/>
       <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="148"/>
-      <c r="C10" s="148"/>
+      <c r="B10" s="153"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="24"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="148"/>
-      <c r="C11" s="148"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="153"/>
       <c r="D11" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="146" t="s">
+      <c r="A13" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="147" t="s">
+      <c r="D13" s="144" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="9">
@@ -10549,19 +10547,19 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="146"/>
-      <c r="B14" s="146"/>
-      <c r="C14" s="146"/>
-      <c r="D14" s="147"/>
+      <c r="A14" s="150"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="144"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="149" t="s">
+      <c r="A15" s="154" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="149"/>
-      <c r="C15" s="149"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
       <c r="D15" s="26"/>
-      <c r="E15" s="159" t="s">
+      <c r="E15" s="156" t="s">
         <v>254</v>
       </c>
     </row>
@@ -10575,48 +10573,48 @@
       <c r="C16" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="D16" s="115"/>
-      <c r="E16" s="159"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="156"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="161" t="s">
+      <c r="A17" s="167" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="162"/>
+      <c r="B17" s="168"/>
       <c r="C17" s="17"/>
       <c r="D17" s="14">
         <v>105000</v>
       </c>
-      <c r="E17" s="159"/>
+      <c r="E17" s="156"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="146" t="s">
+      <c r="A20" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="146" t="s">
+      <c r="C20" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="147" t="s">
+      <c r="D20" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="146"/>
-      <c r="B21" s="146"/>
-      <c r="C21" s="146"/>
-      <c r="D21" s="147"/>
+      <c r="A21" s="150"/>
+      <c r="B21" s="150"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="144"/>
     </row>
     <row r="22" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="145" t="s">
+      <c r="A22" s="149" t="s">
         <v>241</v>
       </c>
-      <c r="B22" s="145"/>
-      <c r="C22" s="145"/>
+      <c r="B22" s="149"/>
+      <c r="C22" s="149"/>
       <c r="D22" s="25"/>
-      <c r="E22" s="160" t="s">
+      <c r="E22" s="169" t="s">
         <v>137</v>
       </c>
     </row>
@@ -10634,7 +10632,7 @@
         <f>30941/2</f>
         <v>15470.5</v>
       </c>
-      <c r="E23" s="160"/>
+      <c r="E23" s="169"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="48">
@@ -10650,7 +10648,7 @@
         <f>42620/2</f>
         <v>21310</v>
       </c>
-      <c r="E24" s="160"/>
+      <c r="E24" s="169"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="48">
@@ -10666,7 +10664,7 @@
         <f>48590/2</f>
         <v>24295</v>
       </c>
-      <c r="E25" s="160"/>
+      <c r="E25" s="169"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="48">
@@ -10682,7 +10680,7 @@
         <f>62797/2</f>
         <v>31398.5</v>
       </c>
-      <c r="E26" s="160"/>
+      <c r="E26" s="169"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="48">
@@ -10698,7 +10696,7 @@
         <f>75511/2</f>
         <v>37755.5</v>
       </c>
-      <c r="E27" s="160"/>
+      <c r="E27" s="169"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="48">
@@ -10714,7 +10712,7 @@
         <f>100661/2</f>
         <v>50330.5</v>
       </c>
-      <c r="E28" s="160"/>
+      <c r="E28" s="169"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="48">
@@ -10730,7 +10728,7 @@
         <f>119146/2</f>
         <v>59573</v>
       </c>
-      <c r="E29" s="160"/>
+      <c r="E29" s="169"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
@@ -10742,18 +10740,18 @@
       <c r="C30" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="D30" s="111">
+      <c r="D30" s="110">
         <f>135880/2</f>
         <v>67940</v>
       </c>
-      <c r="E30" s="160"/>
+      <c r="E30" s="169"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="67"/>
-      <c r="E31" s="160"/>
+      <c r="E31" s="169"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E32" s="22"/>
@@ -10762,37 +10760,37 @@
       <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="146" t="s">
+      <c r="A34" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="146" t="s">
+      <c r="C34" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="147" t="s">
+      <c r="D34" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="E34" s="153" t="s">
+      <c r="E34" s="146" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="146"/>
-      <c r="B35" s="146"/>
-      <c r="C35" s="146"/>
-      <c r="D35" s="147"/>
-      <c r="E35" s="153"/>
+      <c r="A35" s="150"/>
+      <c r="B35" s="150"/>
+      <c r="C35" s="150"/>
+      <c r="D35" s="144"/>
+      <c r="E35" s="146"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="145" t="s">
+      <c r="A36" s="149" t="s">
         <v>242</v>
       </c>
-      <c r="B36" s="145"/>
-      <c r="C36" s="145"/>
+      <c r="B36" s="149"/>
+      <c r="C36" s="149"/>
       <c r="D36" s="25"/>
-      <c r="E36" s="153"/>
+      <c r="E36" s="146"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
@@ -10804,10 +10802,10 @@
       <c r="C37" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D37" s="119">
+      <c r="D37" s="118">
         <v>28194</v>
       </c>
-      <c r="E37" s="153"/>
+      <c r="E37" s="146"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
@@ -10822,7 +10820,7 @@
       <c r="D38" s="81">
         <v>52715.399999999994</v>
       </c>
-      <c r="E38" s="153"/>
+      <c r="E38" s="146"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
@@ -10837,7 +10835,7 @@
       <c r="D39" s="81">
         <v>178343.19999999995</v>
       </c>
-      <c r="E39" s="153"/>
+      <c r="E39" s="146"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
@@ -10849,10 +10847,10 @@
       <c r="C40" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D40" s="109">
+      <c r="D40" s="108">
         <v>104645.19999999995</v>
       </c>
-      <c r="E40" s="153"/>
+      <c r="E40" s="146"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
@@ -10865,33 +10863,33 @@
       <c r="G42" s="55"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" s="146" t="s">
+      <c r="A43" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="146" t="s">
+      <c r="C43" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="147" t="s">
+      <c r="D43" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="146"/>
-      <c r="B44" s="146"/>
-      <c r="C44" s="146"/>
-      <c r="D44" s="147"/>
+      <c r="A44" s="150"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="150"/>
+      <c r="D44" s="144"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="145" t="s">
+      <c r="A45" s="149" t="s">
         <v>243</v>
       </c>
-      <c r="B45" s="145"/>
-      <c r="C45" s="145"/>
+      <c r="B45" s="149"/>
+      <c r="C45" s="149"/>
       <c r="D45" s="25"/>
-      <c r="E45" s="160" t="s">
+      <c r="E45" s="169" t="s">
         <v>27</v>
       </c>
       <c r="G45" s="55"/>
@@ -10909,7 +10907,7 @@
       <c r="D46" s="14">
         <v>6198</v>
       </c>
-      <c r="E46" s="160"/>
+      <c r="E46" s="169"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
@@ -10924,7 +10922,7 @@
       <c r="D47" s="14">
         <v>6781.5</v>
       </c>
-      <c r="E47" s="160"/>
+      <c r="E47" s="169"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
@@ -10939,7 +10937,7 @@
       <c r="D48" s="14">
         <v>8442.5</v>
       </c>
-      <c r="E48" s="160"/>
+      <c r="E48" s="169"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
@@ -10951,10 +10949,10 @@
       <c r="C49" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="14">
-        <v>12205</v>
-      </c>
-      <c r="E49" s="160"/>
+      <c r="D49" s="119">
+        <v>33104</v>
+      </c>
+      <c r="E49" s="169"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
@@ -10967,48 +10965,48 @@
         <v>31</v>
       </c>
       <c r="D50" s="14">
-        <v>12644</v>
-      </c>
-      <c r="E50" s="160"/>
+        <v>44000</v>
+      </c>
+      <c r="E50" s="169"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="D51" s="67"/>
-      <c r="E51" s="160"/>
+      <c r="E51" s="169"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D53" s="6"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B54" s="146" t="s">
+      <c r="A54" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="146" t="s">
+      <c r="C54" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D54" s="147" t="s">
+      <c r="D54" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="146"/>
-      <c r="B55" s="146"/>
-      <c r="C55" s="146"/>
-      <c r="D55" s="147"/>
+      <c r="A55" s="150"/>
+      <c r="B55" s="150"/>
+      <c r="C55" s="150"/>
+      <c r="D55" s="144"/>
     </row>
     <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="145" t="s">
+      <c r="A56" s="149" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="145"/>
-      <c r="C56" s="145"/>
+      <c r="B56" s="149"/>
+      <c r="C56" s="149"/>
       <c r="D56" s="25"/>
-      <c r="E56" s="160" t="s">
+      <c r="E56" s="169" t="s">
         <v>80</v>
       </c>
     </row>
@@ -11025,7 +11023,7 @@
       <c r="D57" s="14">
         <v>4595.5</v>
       </c>
-      <c r="E57" s="160"/>
+      <c r="E57" s="169"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
@@ -11040,7 +11038,7 @@
       <c r="D58" s="14">
         <v>8906.5</v>
       </c>
-      <c r="E58" s="160"/>
+      <c r="E58" s="169"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
@@ -11055,7 +11053,7 @@
       <c r="D59" s="14">
         <v>10470</v>
       </c>
-      <c r="E59" s="160"/>
+      <c r="E59" s="169"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
@@ -11070,7 +11068,7 @@
       <c r="D60" s="14">
         <v>11218.5</v>
       </c>
-      <c r="E60" s="160"/>
+      <c r="E60" s="169"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
@@ -11085,7 +11083,7 @@
       <c r="D61" s="14">
         <v>24616</v>
       </c>
-      <c r="E61" s="160"/>
+      <c r="E61" s="169"/>
     </row>
     <row r="62" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
@@ -11094,33 +11092,33 @@
       <c r="D62" s="67"/>
     </row>
     <row r="64" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" s="146" t="s">
+      <c r="A64" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="146" t="s">
+      <c r="C64" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D64" s="147" t="s">
+      <c r="D64" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="146"/>
-      <c r="B65" s="146"/>
-      <c r="C65" s="146"/>
-      <c r="D65" s="147"/>
+      <c r="A65" s="150"/>
+      <c r="B65" s="150"/>
+      <c r="C65" s="150"/>
+      <c r="D65" s="144"/>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="145" t="s">
+      <c r="A66" s="149" t="s">
         <v>244</v>
       </c>
-      <c r="B66" s="145"/>
-      <c r="C66" s="145"/>
+      <c r="B66" s="149"/>
+      <c r="C66" s="149"/>
       <c r="D66" s="25"/>
-      <c r="E66" s="153" t="s">
+      <c r="E66" s="146" t="s">
         <v>42</v>
       </c>
     </row>
@@ -11137,7 +11135,7 @@
       <c r="D67" s="14">
         <v>8480</v>
       </c>
-      <c r="E67" s="153"/>
+      <c r="E67" s="146"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
@@ -11152,7 +11150,7 @@
       <c r="D68" s="14">
         <v>13028</v>
       </c>
-      <c r="E68" s="153"/>
+      <c r="E68" s="146"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="11">
@@ -11167,7 +11165,7 @@
       <c r="D69" s="14">
         <v>14070.5</v>
       </c>
-      <c r="E69" s="153"/>
+      <c r="E69" s="146"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
@@ -11182,51 +11180,51 @@
       <c r="D70" s="14">
         <v>23773</v>
       </c>
-      <c r="E70" s="153"/>
+      <c r="E70" s="146"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="67"/>
-      <c r="E71" s="153"/>
+      <c r="E71" s="146"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B73" s="146" t="s">
+      <c r="A73" s="150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B73" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="C73" s="146" t="s">
+      <c r="C73" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="D73" s="147" t="s">
+      <c r="D73" s="144" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="146"/>
-      <c r="B74" s="146"/>
-      <c r="C74" s="146"/>
-      <c r="D74" s="147"/>
-      <c r="E74" s="154" t="s">
+      <c r="A74" s="150"/>
+      <c r="B74" s="150"/>
+      <c r="C74" s="150"/>
+      <c r="D74" s="144"/>
+      <c r="E74" s="147" t="s">
         <v>51</v>
       </c>
-      <c r="F74" s="153"/>
+      <c r="F74" s="146"/>
     </row>
     <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="145" t="s">
+      <c r="A75" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="B75" s="145"/>
-      <c r="C75" s="145"/>
+      <c r="B75" s="149"/>
+      <c r="C75" s="149"/>
       <c r="D75" s="25"/>
-      <c r="E75" s="154"/>
-      <c r="F75" s="153"/>
+      <c r="E75" s="147"/>
+      <c r="F75" s="146"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="11">
@@ -11241,8 +11239,8 @@
       <c r="D76" s="14">
         <v>1232</v>
       </c>
-      <c r="E76" s="154"/>
-      <c r="F76" s="153"/>
+      <c r="E76" s="147"/>
+      <c r="F76" s="146"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
@@ -11257,26 +11255,26 @@
       <c r="D77" s="14">
         <v>720</v>
       </c>
-      <c r="E77" s="154"/>
-      <c r="F77" s="153"/>
+      <c r="E77" s="147"/>
+      <c r="F77" s="146"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="11"/>
       <c r="B78" s="11"/>
       <c r="C78" s="11"/>
       <c r="D78" s="67"/>
-      <c r="E78" s="154"/>
-      <c r="F78" s="153"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="146"/>
     </row>
     <row r="80" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
-      <c r="C80" s="107" t="s">
+      <c r="C80" s="106" t="s">
         <v>54</v>
       </c>
       <c r="F80" s="4"/>
     </row>
     <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="107" t="s">
+      <c r="C91" s="106" t="s">
         <v>59</v>
       </c>
     </row>
@@ -11297,31 +11295,11 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="F74:F78"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="E74:E78"/>
-    <mergeCell ref="E66:E71"/>
-    <mergeCell ref="E56:E61"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="E45:E51"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="E22:E31"/>
@@ -11337,11 +11315,31 @@
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E56:E61"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="E45:E51"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="F74:F78"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="E74:E78"/>
+    <mergeCell ref="E66:E71"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11364,31 +11362,31 @@
   </cols>
   <sheetData>
     <row r="19" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="B19" s="148" t="s">
+      <c r="B19" s="153" t="s">
         <v>168</v>
       </c>
-      <c r="C19" s="148"/>
+      <c r="C19" s="153"/>
       <c r="D19" s="24"/>
     </row>
     <row r="20" spans="1:59" x14ac:dyDescent="0.25">
-      <c r="B20" s="148"/>
-      <c r="C20" s="148"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="153"/>
       <c r="D20" s="24"/>
     </row>
     <row r="23" spans="1:59" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="146" t="s">
+      <c r="A23" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="146" t="s">
+      <c r="B23" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="146" t="s">
+      <c r="C23" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="146" t="s">
+      <c r="D23" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="146"/>
+      <c r="E23" s="150"/>
       <c r="F23"/>
       <c r="G23"/>
       <c r="H23"/>
@@ -11445,11 +11443,11 @@
       <c r="BG23"/>
     </row>
     <row r="24" spans="1:59" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="146"/>
-      <c r="B24" s="146"/>
-      <c r="C24" s="146"/>
-      <c r="D24" s="146"/>
-      <c r="E24" s="146"/>
+      <c r="A24" s="150"/>
+      <c r="B24" s="150"/>
+      <c r="C24" s="150"/>
+      <c r="D24" s="150"/>
+      <c r="E24" s="150"/>
       <c r="F24"/>
       <c r="G24"/>
       <c r="H24"/>
@@ -11507,11 +11505,11 @@
     </row>
     <row r="25" spans="1:59" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:59" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="146" t="s">
+      <c r="A26" s="150" t="s">
         <v>169</v>
       </c>
-      <c r="B26" s="146"/>
-      <c r="C26" s="146"/>
+      <c r="B26" s="150"/>
+      <c r="C26" s="150"/>
       <c r="D26" s="23" t="s">
         <v>5</v>
       </c>
@@ -11565,11 +11563,11 @@
       <c r="D30" s="10"/>
     </row>
     <row r="31" spans="1:59" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="146" t="s">
+      <c r="A31" s="150" t="s">
         <v>170</v>
       </c>
-      <c r="B31" s="146"/>
-      <c r="C31" s="146"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="150"/>
       <c r="D31" s="23" t="s">
         <v>5</v>
       </c>
@@ -11584,7 +11582,7 @@
       <c r="C32" s="16">
         <v>36395</v>
       </c>
-      <c r="D32" s="115">
+      <c r="D32" s="114">
         <f>42050/2</f>
         <v>21025</v>
       </c>
@@ -11599,7 +11597,7 @@
       <c r="C33" s="16">
         <v>58852</v>
       </c>
-      <c r="D33" s="115">
+      <c r="D33" s="114">
         <f>68125/2</f>
         <v>34062.5</v>
       </c>
@@ -11614,7 +11612,7 @@
       <c r="C34" s="16">
         <v>86492</v>
       </c>
-      <c r="D34" s="115">
+      <c r="D34" s="114">
         <f>100075/2</f>
         <v>50037.5</v>
       </c>
@@ -11623,11 +11621,11 @@
       <c r="D35" s="10"/>
     </row>
     <row r="36" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="146" t="s">
+      <c r="A36" s="150" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="146"/>
-      <c r="C36" s="146"/>
+      <c r="B36" s="150"/>
+      <c r="C36" s="150"/>
       <c r="D36" s="23" t="s">
         <v>5</v>
       </c>
@@ -11681,11 +11679,11 @@
       <c r="D40" s="10"/>
     </row>
     <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="146" t="s">
+      <c r="A41" s="150" t="s">
         <v>184</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="150"/>
       <c r="D41" s="23" t="s">
         <v>5</v>
       </c>
@@ -11700,7 +11698,7 @@
       <c r="C42" s="16">
         <v>7201</v>
       </c>
-      <c r="D42" s="115">
+      <c r="D42" s="114">
         <f>9456/2</f>
         <v>4728</v>
       </c>
@@ -11715,7 +11713,7 @@
       <c r="C43" s="16">
         <v>8074</v>
       </c>
-      <c r="D43" s="115">
+      <c r="D43" s="114">
         <f>7864/2</f>
         <v>3932</v>
       </c>
@@ -11730,7 +11728,7 @@
       <c r="C44" s="16">
         <v>7864</v>
       </c>
-      <c r="D44" s="115">
+      <c r="D44" s="114">
         <f>7864/2</f>
         <v>3932</v>
       </c>
@@ -11745,7 +11743,7 @@
       <c r="C45" s="16">
         <v>29621</v>
       </c>
-      <c r="D45" s="115">
+      <c r="D45" s="114">
         <f>33523/2</f>
         <v>16761.5</v>
       </c>
@@ -11760,7 +11758,7 @@
       <c r="C46" s="16">
         <v>4231</v>
       </c>
-      <c r="D46" s="115">
+      <c r="D46" s="114">
         <f>4359/2</f>
         <v>2179.5</v>
       </c>
@@ -11775,7 +11773,7 @@
       <c r="C47" s="16">
         <v>5959</v>
       </c>
-      <c r="D47" s="115">
+      <c r="D47" s="114">
         <f>5969/2</f>
         <v>2984.5</v>
       </c>
@@ -11790,7 +11788,7 @@
       <c r="C48" s="16">
         <v>16316</v>
       </c>
-      <c r="D48" s="115">
+      <c r="D48" s="114">
         <f>16316/2</f>
         <v>8158</v>
       </c>
@@ -11805,7 +11803,7 @@
       <c r="C49" s="16">
         <v>5401</v>
       </c>
-      <c r="D49" s="115">
+      <c r="D49" s="114">
         <f>5401/2</f>
         <v>2700.5</v>
       </c>
@@ -11820,7 +11818,7 @@
       <c r="C50" s="16">
         <v>6197</v>
       </c>
-      <c r="D50" s="115">
+      <c r="D50" s="114">
         <f>6197/2</f>
         <v>3098.5</v>
       </c>
@@ -11835,7 +11833,7 @@
       <c r="C51" s="16">
         <v>33755</v>
       </c>
-      <c r="D51" s="115">
+      <c r="D51" s="114">
         <f>33755/2</f>
         <v>16877.5</v>
       </c>
@@ -11850,7 +11848,7 @@
       <c r="C52" s="16">
         <v>32954</v>
       </c>
-      <c r="D52" s="115">
+      <c r="D52" s="114">
         <f>32954/2</f>
         <v>16477</v>
       </c>
@@ -11863,15 +11861,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B19:C20"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
     <mergeCell ref="D23:E24"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="B19:C20"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
